--- a/data/exports/football-recap-master.xlsx
+++ b/data/exports/football-recap-master.xlsx
@@ -8083,44 +8083,44 @@
         </is>
       </c>
       <c r="K79">
-        <v>0.4032</v>
+        <v>0.3836</v>
       </c>
       <c r="L79">
-        <v>0.3008</v>
+        <v>0.3107</v>
       </c>
       <c r="M79">
-        <v>0.2961</v>
+        <v>0.3057</v>
       </c>
       <c r="N79">
-        <v>0.4032</v>
+        <v>0.3836</v>
       </c>
       <c r="O79">
-        <v>0.3008</v>
+        <v>0.3107</v>
       </c>
       <c r="P79">
-        <v>0.2961</v>
+        <v>0.3057</v>
       </c>
       <c r="Q79">
-        <v>0.4666</v>
+        <v>0.4418</v>
       </c>
       <c r="R79">
-        <v>0.2588</v>
+        <v>0.2611</v>
       </c>
       <c r="S79">
-        <v>0.2747</v>
+        <v>0.2972</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1-1:12.3% / 1-0:10.6% / 2-1:9.2%</t>
+          <t>1-1:12.5% / 1-0:10.7% / 2-1:9%</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V79">
-        <v>31.25</v>
+        <v>25.43</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>经模型综合分析：澳超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：澳超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11744,42 +11744,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K109">
-        <v>0.2543</v>
+        <v>0.7045</v>
       </c>
       <c r="L109">
-        <v>0.2447</v>
+        <v>0.1655</v>
       </c>
       <c r="M109">
-        <v>0.501</v>
+        <v>0.13</v>
       </c>
       <c r="N109">
         <v>0.2543</v>
@@ -11810,7 +11810,7 @@
         </is>
       </c>
       <c r="V109">
-        <v>48.48</v>
+        <v>92.23</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11867,42 +11867,42 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="K110">
-        <v>0.627</v>
+        <v>0.2785</v>
       </c>
       <c r="L110">
-        <v>0.2197</v>
+        <v>0.253</v>
       </c>
       <c r="M110">
-        <v>0.1532</v>
+        <v>0.4685</v>
       </c>
       <c r="N110">
         <v>0.627</v>
@@ -11933,7 +11933,7 @@
         </is>
       </c>
       <c r="V110">
-        <v>72</v>
+        <v>42.08</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12019,13 +12019,13 @@
         </is>
       </c>
       <c r="K111">
-        <v>0.4947</v>
+        <v>0.6014</v>
       </c>
       <c r="L111">
-        <v>0.2664</v>
+        <v>0.2297</v>
       </c>
       <c r="M111">
-        <v>0.239</v>
+        <v>0.1689</v>
       </c>
       <c r="N111">
         <v>0.4947</v>
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="V111">
-        <v>46.37</v>
+        <v>69.75</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -12142,13 +12142,13 @@
         </is>
       </c>
       <c r="K112">
-        <v>0.3949</v>
+        <v>0.5438</v>
       </c>
       <c r="L112">
-        <v>0.3331</v>
+        <v>0.2578</v>
       </c>
       <c r="M112">
-        <v>0.272</v>
+        <v>0.1984</v>
       </c>
       <c r="N112">
         <v>0.3949</v>
@@ -12175,11 +12175,11 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V112">
-        <v>22.44</v>
+        <v>57.89</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -12265,13 +12265,13 @@
         </is>
       </c>
       <c r="K113">
-        <v>0.5101</v>
+        <v>0.3719</v>
       </c>
       <c r="L113">
-        <v>0.2496</v>
+        <v>0.3471</v>
       </c>
       <c r="M113">
-        <v>0.2402</v>
+        <v>0.281</v>
       </c>
       <c r="N113">
         <v>0.5101</v>
@@ -12298,11 +12298,11 @@
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V113">
-        <v>50.37</v>
+        <v>18.51</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -12384,17 +12384,17 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K114">
-        <v>0.4605</v>
+        <v>0.5348</v>
       </c>
       <c r="L114">
-        <v>0.2536</v>
+        <v>0.2446</v>
       </c>
       <c r="M114">
-        <v>0.2859</v>
+        <v>0.2206</v>
       </c>
       <c r="N114">
         <v>0.4605</v>
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="V114">
-        <v>39.07</v>
+        <v>57.62</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12511,13 +12511,13 @@
         </is>
       </c>
       <c r="K115">
-        <v>0.3999</v>
+        <v>0.4352</v>
       </c>
       <c r="L115">
-        <v>0.2717</v>
+        <v>0.2643</v>
       </c>
       <c r="M115">
-        <v>0.3284</v>
+        <v>0.3005</v>
       </c>
       <c r="N115">
         <v>0.3999</v>
@@ -12544,11 +12544,11 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V115">
-        <v>23.68</v>
+        <v>36.46</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12757,13 +12757,13 @@
         </is>
       </c>
       <c r="K117">
-        <v>0.443</v>
+        <v>0.4872</v>
       </c>
       <c r="L117">
-        <v>0.2916</v>
+        <v>0.2814</v>
       </c>
       <c r="M117">
-        <v>0.2655</v>
+        <v>0.2314</v>
       </c>
       <c r="N117">
         <v>0.443</v>
@@ -12794,7 +12794,7 @@
         </is>
       </c>
       <c r="V117">
-        <v>35.72</v>
+        <v>46.6</v>
       </c>
       <c r="W117" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -12876,17 +12876,17 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="K118">
-        <v>0.521</v>
+        <v>0.5009</v>
       </c>
       <c r="L118">
-        <v>0.2408</v>
+        <v>0.2465</v>
       </c>
       <c r="M118">
-        <v>0.2382</v>
+        <v>0.2526</v>
       </c>
       <c r="N118">
         <v>0.521</v>
@@ -12917,7 +12917,7 @@
         </is>
       </c>
       <c r="V118">
-        <v>52.93</v>
+        <v>51.41</v>
       </c>
       <c r="W118" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13003,13 +13003,13 @@
         </is>
       </c>
       <c r="K119">
-        <v>0.4923</v>
+        <v>0.4828</v>
       </c>
       <c r="L119">
-        <v>0.2635</v>
+        <v>0.272</v>
       </c>
       <c r="M119">
-        <v>0.2441</v>
+        <v>0.2452</v>
       </c>
       <c r="N119">
         <v>0.4923</v>
@@ -13040,7 +13040,7 @@
         </is>
       </c>
       <c r="V119">
-        <v>46.24</v>
+        <v>46.73</v>
       </c>
       <c r="W119" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -13126,13 +13126,13 @@
         </is>
       </c>
       <c r="K120">
-        <v>0.5759</v>
+        <v>0.5934</v>
       </c>
       <c r="L120">
-        <v>0.2432</v>
+        <v>0.2361</v>
       </c>
       <c r="M120">
-        <v>0.181</v>
+        <v>0.1705</v>
       </c>
       <c r="N120">
         <v>0.5759</v>
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="V120">
-        <v>61.61</v>
+        <v>67.88</v>
       </c>
       <c r="W120" t="inlineStr">
         <is>
@@ -13178,7 +13178,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13249,13 +13249,13 @@
         </is>
       </c>
       <c r="K121">
-        <v>0.369</v>
+        <v>0.3731</v>
       </c>
       <c r="L121">
-        <v>0.2689</v>
+        <v>0.2676</v>
       </c>
       <c r="M121">
-        <v>0.362</v>
+        <v>0.3593</v>
       </c>
       <c r="N121">
         <v>0.369</v>
@@ -13286,7 +13286,7 @@
         </is>
       </c>
       <c r="V121">
-        <v>15.65</v>
+        <v>19.36</v>
       </c>
       <c r="W121" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">

--- a/data/exports/football-recap-master.xlsx
+++ b/data/exports/football-recap-master.xlsx
@@ -8039,17 +8039,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>周六002</t>
+          <t>周六006</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>澳超</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>奥克兰FC 对 悉尼FC</t>
+          <t>哈尔姆斯 对 厄格里特</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8083,44 +8083,44 @@
         </is>
       </c>
       <c r="K79">
-        <v>0.3836</v>
+        <v>0.4454</v>
       </c>
       <c r="L79">
-        <v>0.3107</v>
+        <v>0.2859</v>
       </c>
       <c r="M79">
-        <v>0.3057</v>
+        <v>0.2686</v>
       </c>
       <c r="N79">
-        <v>0.3836</v>
+        <v>0.4454</v>
       </c>
       <c r="O79">
-        <v>0.3107</v>
+        <v>0.2859</v>
       </c>
       <c r="P79">
-        <v>0.3057</v>
+        <v>0.2686</v>
       </c>
       <c r="Q79">
-        <v>0.4418</v>
+        <v>0.5477</v>
       </c>
       <c r="R79">
-        <v>0.2611</v>
+        <v>0.2382</v>
       </c>
       <c r="S79">
-        <v>0.2972</v>
+        <v>0.2141</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1-1:12.5% / 1-0:10.7% / 2-1:9%</t>
+          <t>1-1:11.7% / 1-0:11.5% / 2-0:10.2%</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V79">
-        <v>25.43</v>
+        <v>37.67</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -8128,14 +8128,14 @@
         </is>
       </c>
       <c r="X79">
-        <v>-0.0525</v>
+        <v>-0.1137</v>
       </c>
       <c r="Y79">
         <v>0</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>经模型综合分析：澳超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8162,17 +8162,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>周六003</t>
+          <t>周六007</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>日职</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>柏太阳神 对 千叶市原</t>
+          <t>卡尔马 对 代格福什</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8187,17 +8187,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8206,35 +8206,35 @@
         </is>
       </c>
       <c r="K80">
-        <v>0.6324</v>
+        <v>0.4872</v>
       </c>
       <c r="L80">
-        <v>0.2236</v>
+        <v>0.2814</v>
       </c>
       <c r="M80">
-        <v>0.144</v>
+        <v>0.2314</v>
       </c>
       <c r="N80">
-        <v>0.6324</v>
+        <v>0.4872</v>
       </c>
       <c r="O80">
-        <v>0.2236</v>
+        <v>0.2814</v>
       </c>
       <c r="P80">
-        <v>0.144</v>
+        <v>0.2314</v>
       </c>
       <c r="Q80">
-        <v>0.705</v>
+        <v>0.6213</v>
       </c>
       <c r="R80">
-        <v>0.1848</v>
+        <v>0.2177</v>
       </c>
       <c r="S80">
-        <v>0.1103</v>
+        <v>0.1611</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>2-0:12.9% / 1-0:11.9% / 2-1:9.7%</t>
+          <t>1-0:12.3% / 2-0:11.4% / 1-1:10.2%</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="V80">
-        <v>73.57</v>
+        <v>46.6</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -8251,14 +8251,14 @@
         </is>
       </c>
       <c r="X80">
-        <v>-0.1146</v>
+        <v>-0.0743</v>
       </c>
       <c r="Y80">
         <v>0</v>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>周六004</t>
+          <t>周六008</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>日职</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>京都 对 长崎航海</t>
+          <t>坦山猫 对 赫尔火花</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8325,39 +8325,39 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K81">
-        <v>0.4635</v>
+        <v>0.5009</v>
       </c>
       <c r="L81">
-        <v>0.2699</v>
+        <v>0.2465</v>
       </c>
       <c r="M81">
-        <v>0.2666</v>
+        <v>0.2526</v>
       </c>
       <c r="N81">
-        <v>0.4635</v>
+        <v>0.5009</v>
       </c>
       <c r="O81">
-        <v>0.2699</v>
+        <v>0.2465</v>
       </c>
       <c r="P81">
-        <v>0.2666</v>
+        <v>0.2526</v>
       </c>
       <c r="Q81">
-        <v>0.5636</v>
+        <v>0.6198</v>
       </c>
       <c r="R81">
-        <v>0.2354</v>
+        <v>0.2187</v>
       </c>
       <c r="S81">
-        <v>0.2011</v>
+        <v>0.1616</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1-0:11.8% / 1-1:11.2% / 2-0:10.1%</t>
+          <t>1-0:12.1% / 2-0:11.5% / 1-1:10.5%</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="V81">
-        <v>42.05</v>
+        <v>51.41</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8374,14 +8374,14 @@
         </is>
       </c>
       <c r="X81">
-        <v>-0.1147</v>
+        <v>-0.0638</v>
       </c>
       <c r="Y81">
         <v>0</v>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>经模型综合分析：日职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>周六005</t>
+          <t>周六009</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>国际图尔 对 TPS图尔</t>
+          <t>塞伊奈 对 AC奥卢</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8428,68 +8428,68 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="K82">
-        <v>0.6414</v>
+        <v>0.3731</v>
       </c>
       <c r="L82">
-        <v>0.2157</v>
+        <v>0.2676</v>
       </c>
       <c r="M82">
-        <v>0.1429</v>
+        <v>0.3593</v>
       </c>
       <c r="N82">
-        <v>0.6414</v>
+        <v>0.3731</v>
       </c>
       <c r="O82">
-        <v>0.2157</v>
+        <v>0.2676</v>
       </c>
       <c r="P82">
-        <v>0.1429</v>
+        <v>0.3593</v>
       </c>
       <c r="Q82">
-        <v>0.7105</v>
+        <v>0.3832</v>
       </c>
       <c r="R82">
-        <v>0.1798</v>
+        <v>0.2598</v>
       </c>
       <c r="S82">
-        <v>0.1098</v>
+        <v>0.3571</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2-0:13.2% / 1-0:11.9% / 3-0:9.4%</t>
+          <t>1-1:12.6% / 1-0:10% / 0-1:9%</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V82">
-        <v>77.49</v>
+        <v>19.36</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>周六006</t>
+          <t>周六010</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>哈尔姆斯 对 厄格里特</t>
+          <t>库奥皮奥 对 拉赫蒂</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8575,35 +8575,35 @@
         </is>
       </c>
       <c r="K83">
-        <v>0.4742</v>
+        <v>0.5934</v>
       </c>
       <c r="L83">
-        <v>0.2687</v>
+        <v>0.2361</v>
       </c>
       <c r="M83">
-        <v>0.257</v>
+        <v>0.1705</v>
       </c>
       <c r="N83">
-        <v>0.4742</v>
+        <v>0.5934</v>
       </c>
       <c r="O83">
-        <v>0.2687</v>
+        <v>0.2361</v>
       </c>
       <c r="P83">
-        <v>0.257</v>
+        <v>0.1705</v>
       </c>
       <c r="Q83">
-        <v>0.5913</v>
+        <v>0.7053</v>
       </c>
       <c r="R83">
-        <v>0.2268</v>
+        <v>0.1834</v>
       </c>
       <c r="S83">
-        <v>0.1819</v>
+        <v>0.1114</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1-0:11.8% / 1-1:11% / 2-0:10.9%</t>
+          <t>2-0:13.1% / 1-0:11.9% / 3-0:9.6%</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="V83">
-        <v>43.89</v>
+        <v>67.88</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8620,14 +8620,14 @@
         </is>
       </c>
       <c r="X83">
-        <v>-0.1132</v>
+        <v>-0.0743</v>
       </c>
       <c r="Y83">
         <v>0</v>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8654,17 +8654,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>周六007</t>
+          <t>周六011</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>卡尔马 对 代格福什</t>
+          <t>雅罗 对 玛丽港</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8698,35 +8698,35 @@
         </is>
       </c>
       <c r="K84">
-        <v>0.4872</v>
+        <v>0.4828</v>
       </c>
       <c r="L84">
-        <v>0.2814</v>
+        <v>0.272</v>
       </c>
       <c r="M84">
-        <v>0.2314</v>
+        <v>0.2452</v>
       </c>
       <c r="N84">
-        <v>0.4872</v>
+        <v>0.4828</v>
       </c>
       <c r="O84">
-        <v>0.2814</v>
+        <v>0.272</v>
       </c>
       <c r="P84">
-        <v>0.2314</v>
+        <v>0.2452</v>
       </c>
       <c r="Q84">
-        <v>0.6213</v>
+        <v>0.6085</v>
       </c>
       <c r="R84">
-        <v>0.2177</v>
+        <v>0.2202</v>
       </c>
       <c r="S84">
-        <v>0.1611</v>
+        <v>0.1714</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1-0:12.3% / 2-0:11.4% / 1-1:10.2%</t>
+          <t>1-0:11.7% / 2-0:11.1% / 1-1:10.5%</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="V84">
-        <v>46.6</v>
+        <v>46.73</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8743,14 +8743,14 @@
         </is>
       </c>
       <c r="X84">
-        <v>-0.0743</v>
+        <v>-0.0779</v>
       </c>
       <c r="Y84">
         <v>0</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -8777,79 +8777,79 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>周六008</t>
+          <t>周六012</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>坦山猫 对 赫尔火花</t>
+          <t>赫尔城 对 米堡</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K85">
-        <v>0.5009</v>
+        <v>0.2231</v>
       </c>
       <c r="L85">
-        <v>0.2465</v>
+        <v>0.2904</v>
       </c>
       <c r="M85">
-        <v>0.2526</v>
+        <v>0.4866</v>
       </c>
       <c r="N85">
-        <v>0.5009</v>
+        <v>0.2231</v>
       </c>
       <c r="O85">
-        <v>0.2465</v>
+        <v>0.2904</v>
       </c>
       <c r="P85">
-        <v>0.2526</v>
+        <v>0.4866</v>
       </c>
       <c r="Q85">
-        <v>0.6198</v>
+        <v>0.1558</v>
       </c>
       <c r="R85">
-        <v>0.2187</v>
+        <v>0.214</v>
       </c>
       <c r="S85">
-        <v>0.1616</v>
+        <v>0.6303</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1-0:12.1% / 2-0:11.5% / 1-1:10.5%</t>
+          <t>0-1:12.3% / 0-2:11.9% / 1-2:10.1%</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="V85">
-        <v>51.41</v>
+        <v>43.94</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8866,14 +8866,14 @@
         </is>
       </c>
       <c r="X85">
-        <v>-0.0638</v>
+        <v>-0.1144</v>
       </c>
       <c r="Y85">
         <v>0</v>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：英冠，客胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -8900,88 +8900,88 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>周六009</t>
+          <t>周六013</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>塞伊奈 对 AC奥卢</t>
+          <t>博洛尼亚 对 国际米兰</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>主胜-客胜</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>客胜-主胜</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>主胜-客胜</t>
-        </is>
-      </c>
       <c r="K86">
-        <v>0.3731</v>
+        <v>0.2785</v>
       </c>
       <c r="L86">
-        <v>0.2676</v>
+        <v>0.253</v>
       </c>
       <c r="M86">
-        <v>0.3593</v>
+        <v>0.4685</v>
       </c>
       <c r="N86">
-        <v>0.3731</v>
+        <v>0.2785</v>
       </c>
       <c r="O86">
-        <v>0.2676</v>
+        <v>0.253</v>
       </c>
       <c r="P86">
-        <v>0.3593</v>
+        <v>0.4685</v>
       </c>
       <c r="Q86">
-        <v>0.3832</v>
+        <v>0.2088</v>
       </c>
       <c r="R86">
-        <v>0.2598</v>
+        <v>0.2331</v>
       </c>
       <c r="S86">
-        <v>0.3571</v>
+        <v>0.5582</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1-1:12.6% / 1-0:10% / 0-1:9%</t>
+          <t>1-1:11.3% / 0-1:10.9% / 0-2:10.2%</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V86">
-        <v>19.36</v>
+        <v>42.08</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="X86">
-        <v>-0.0777</v>
+        <v>-0.1145</v>
       </c>
       <c r="Y86">
         <v>0</v>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9023,17 +9023,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>周六010</t>
+          <t>周六014</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>德国杯</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>库奥皮奥 对 拉赫蒂</t>
+          <t>拜仁 对 斯图加特</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9067,35 +9067,35 @@
         </is>
       </c>
       <c r="K87">
-        <v>0.5934</v>
+        <v>0.7045</v>
       </c>
       <c r="L87">
-        <v>0.2361</v>
+        <v>0.1655</v>
       </c>
       <c r="M87">
-        <v>0.1705</v>
+        <v>0.13</v>
       </c>
       <c r="N87">
-        <v>0.5934</v>
+        <v>0.7045</v>
       </c>
       <c r="O87">
-        <v>0.2361</v>
+        <v>0.1655</v>
       </c>
       <c r="P87">
-        <v>0.1705</v>
+        <v>0.13</v>
       </c>
       <c r="Q87">
-        <v>0.7053</v>
+        <v>0.711</v>
       </c>
       <c r="R87">
-        <v>0.1834</v>
+        <v>0.1764</v>
       </c>
       <c r="S87">
-        <v>0.1114</v>
+        <v>0.1127</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2-0:13.1% / 1-0:11.9% / 3-0:9.6%</t>
+          <t>2-0:12.6% / 1-0:11.1% / 2-1:9.7%</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="V87">
-        <v>67.88</v>
+        <v>92.23</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
@@ -9112,14 +9112,14 @@
         </is>
       </c>
       <c r="X87">
-        <v>-0.0743</v>
+        <v>-0.063</v>
       </c>
       <c r="Y87">
         <v>0</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>周六011</t>
+          <t>周六015</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>荷乙</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>雅罗 对 玛丽港</t>
+          <t>福伦丹 对 威廉二世</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9186,39 +9186,39 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="K88">
-        <v>0.4828</v>
+        <v>0.4352</v>
       </c>
       <c r="L88">
-        <v>0.272</v>
+        <v>0.2643</v>
       </c>
       <c r="M88">
-        <v>0.2452</v>
+        <v>0.3005</v>
       </c>
       <c r="N88">
-        <v>0.4828</v>
+        <v>0.4352</v>
       </c>
       <c r="O88">
-        <v>0.272</v>
+        <v>0.2643</v>
       </c>
       <c r="P88">
-        <v>0.2452</v>
+        <v>0.3005</v>
       </c>
       <c r="Q88">
-        <v>0.6085</v>
+        <v>0.504</v>
       </c>
       <c r="R88">
-        <v>0.2202</v>
+        <v>0.2456</v>
       </c>
       <c r="S88">
-        <v>0.1714</v>
+        <v>0.2504</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1-0:11.7% / 2-0:11.1% / 1-1:10.5%</t>
+          <t>1-1:11.7% / 1-0:10.9% / 2-1:9.8%</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="V88">
-        <v>46.73</v>
+        <v>36.46</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -9235,14 +9235,14 @@
         </is>
       </c>
       <c r="X88">
-        <v>-0.0779</v>
+        <v>-0.0774</v>
       </c>
       <c r="Y88">
         <v>0</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9269,22 +9269,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>周六012</t>
+          <t>周六016</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>赫尔城 对 米堡</t>
+          <t>拉齐奥 对 比萨</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9294,54 +9294,54 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>客胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K89">
-        <v>0.2159</v>
+        <v>0.6014</v>
       </c>
       <c r="L89">
-        <v>0.2811</v>
+        <v>0.2297</v>
       </c>
       <c r="M89">
-        <v>0.503</v>
+        <v>0.1689</v>
       </c>
       <c r="N89">
-        <v>0.2159</v>
+        <v>0.6014</v>
       </c>
       <c r="O89">
-        <v>0.2811</v>
+        <v>0.2297</v>
       </c>
       <c r="P89">
-        <v>0.503</v>
+        <v>0.1689</v>
       </c>
       <c r="Q89">
-        <v>0.1396</v>
+        <v>0.7064</v>
       </c>
       <c r="R89">
-        <v>0.2048</v>
+        <v>0.1832</v>
       </c>
       <c r="S89">
-        <v>0.6557</v>
+        <v>0.1105</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>0-1:12.5% / 0-2:12.3% / 1-2:9.7%</t>
+          <t>2-0:13.5% / 1-0:11.9% / 2-1:9.8%</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9350,7 +9350,7 @@
         </is>
       </c>
       <c r="V89">
-        <v>47.44</v>
+        <v>69.75</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -9358,14 +9358,14 @@
         </is>
       </c>
       <c r="X89">
-        <v>-0.1147</v>
+        <v>-0.0558</v>
       </c>
       <c r="Y89">
         <v>0</v>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>经模型综合分析：英冠，客胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9392,79 +9392,79 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>周六013</t>
+          <t>周六017</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>博洛尼亚 对 国际米兰</t>
+          <t>赫罗纳 对 埃尔切</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K90">
-        <v>0.2785</v>
+        <v>0.5348</v>
       </c>
       <c r="L90">
-        <v>0.253</v>
+        <v>0.2446</v>
       </c>
       <c r="M90">
-        <v>0.4685</v>
+        <v>0.2206</v>
       </c>
       <c r="N90">
-        <v>0.2785</v>
+        <v>0.5348</v>
       </c>
       <c r="O90">
-        <v>0.253</v>
+        <v>0.2446</v>
       </c>
       <c r="P90">
-        <v>0.4685</v>
+        <v>0.2206</v>
       </c>
       <c r="Q90">
-        <v>0.2088</v>
+        <v>0.6805</v>
       </c>
       <c r="R90">
-        <v>0.2331</v>
+        <v>0.1961</v>
       </c>
       <c r="S90">
-        <v>0.5582</v>
+        <v>0.1235</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1-1:11.3% / 0-1:10.9% / 0-2:10.2%</t>
+          <t>2-0:12.7% / 1-0:12.1% / 1-1:9.5%</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="V90">
-        <v>42.08</v>
+        <v>57.62</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9481,14 +9481,14 @@
         </is>
       </c>
       <c r="X90">
-        <v>-0.1145</v>
+        <v>-0.0534</v>
       </c>
       <c r="Y90">
         <v>0</v>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9515,17 +9515,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>周六014</t>
+          <t>周六018</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>德国杯</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>拜仁 对 斯图加特</t>
+          <t>马洛卡 对 奥维耶多</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9559,35 +9559,35 @@
         </is>
       </c>
       <c r="K91">
-        <v>0.7045</v>
+        <v>0.6344</v>
       </c>
       <c r="L91">
-        <v>0.1655</v>
+        <v>0.2207</v>
       </c>
       <c r="M91">
-        <v>0.13</v>
+        <v>0.1449</v>
       </c>
       <c r="N91">
-        <v>0.7045</v>
+        <v>0.6344</v>
       </c>
       <c r="O91">
-        <v>0.1655</v>
+        <v>0.2207</v>
       </c>
       <c r="P91">
-        <v>0.13</v>
+        <v>0.1449</v>
       </c>
       <c r="Q91">
-        <v>0.711</v>
+        <v>0.7056</v>
       </c>
       <c r="R91">
-        <v>0.1764</v>
+        <v>0.1837</v>
       </c>
       <c r="S91">
-        <v>0.1127</v>
+        <v>0.1108</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2-0:12.6% / 1-0:11.1% / 2-1:9.7%</t>
+          <t>2-0:13% / 1-0:11.6% / 3-0:9.7%</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="V91">
-        <v>92.23</v>
+        <v>75.91</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9604,14 +9604,14 @@
         </is>
       </c>
       <c r="X91">
-        <v>-0.063</v>
+        <v>-0.07</v>
       </c>
       <c r="Y91">
         <v>0</v>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9638,17 +9638,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>周六015</t>
+          <t>周六019</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>福伦丹 对 威廉二世</t>
+          <t>西班牙人 对 皇家社会</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9678,39 +9678,39 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K92">
-        <v>0.4352</v>
+        <v>0.4218</v>
       </c>
       <c r="L92">
-        <v>0.2643</v>
+        <v>0.3097</v>
       </c>
       <c r="M92">
-        <v>0.3005</v>
+        <v>0.2684</v>
       </c>
       <c r="N92">
-        <v>0.4352</v>
+        <v>0.4218</v>
       </c>
       <c r="O92">
-        <v>0.2643</v>
+        <v>0.3097</v>
       </c>
       <c r="P92">
-        <v>0.3005</v>
+        <v>0.2684</v>
       </c>
       <c r="Q92">
-        <v>0.504</v>
+        <v>0.5114</v>
       </c>
       <c r="R92">
-        <v>0.2456</v>
+        <v>0.2489</v>
       </c>
       <c r="S92">
-        <v>0.2504</v>
+        <v>0.2398</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1-1:11.7% / 1-0:10.9% / 2-1:9.8%</t>
+          <t>1-1:11.8% / 1-0:11.3% / 2-1:9.4%</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="V92">
-        <v>36.46</v>
+        <v>31.71</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -9727,14 +9727,14 @@
         </is>
       </c>
       <c r="X92">
-        <v>-0.0774</v>
+        <v>-0.1142</v>
       </c>
       <c r="Y92">
         <v>0</v>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9761,17 +9761,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>周六016</t>
+          <t>周六020</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>拉齐奥 对 比萨</t>
+          <t>皇马 对 毕尔巴鄂</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9805,35 +9805,35 @@
         </is>
       </c>
       <c r="K93">
-        <v>0.6014</v>
+        <v>0.6459</v>
       </c>
       <c r="L93">
-        <v>0.2297</v>
+        <v>0.1991</v>
       </c>
       <c r="M93">
-        <v>0.1689</v>
+        <v>0.155</v>
       </c>
       <c r="N93">
-        <v>0.6014</v>
+        <v>0.6459</v>
       </c>
       <c r="O93">
-        <v>0.2297</v>
+        <v>0.1991</v>
       </c>
       <c r="P93">
-        <v>0.1689</v>
+        <v>0.155</v>
       </c>
       <c r="Q93">
-        <v>0.7064</v>
+        <v>0.7118</v>
       </c>
       <c r="R93">
-        <v>0.1832</v>
+        <v>0.1812</v>
       </c>
       <c r="S93">
-        <v>0.1105</v>
+        <v>0.1071</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:11.9% / 2-1:9.8%</t>
+          <t>2-0:13.1% / 1-0:12% / 3-0:9.4%</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="V93">
-        <v>69.75</v>
+        <v>79.72</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -9850,14 +9850,14 @@
         </is>
       </c>
       <c r="X93">
-        <v>-0.0558</v>
+        <v>-0.0731</v>
       </c>
       <c r="Y93">
         <v>0</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>周六017</t>
+          <t>周六021</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>赫罗纳 对 埃尔切</t>
+          <t>赫塔费 对 奥萨苏纳</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9928,44 +9928,44 @@
         </is>
       </c>
       <c r="K94">
-        <v>0.5348</v>
+        <v>0.3645</v>
       </c>
       <c r="L94">
-        <v>0.2446</v>
+        <v>0.3543</v>
       </c>
       <c r="M94">
-        <v>0.2206</v>
+        <v>0.2812</v>
       </c>
       <c r="N94">
-        <v>0.5348</v>
+        <v>0.3645</v>
       </c>
       <c r="O94">
-        <v>0.2446</v>
+        <v>0.3543</v>
       </c>
       <c r="P94">
-        <v>0.2206</v>
+        <v>0.2812</v>
       </c>
       <c r="Q94">
-        <v>0.6805</v>
+        <v>0.444</v>
       </c>
       <c r="R94">
-        <v>0.1961</v>
+        <v>0.2626</v>
       </c>
       <c r="S94">
-        <v>0.1235</v>
+        <v>0.2935</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>2-0:12.7% / 1-0:12.1% / 1-1:9.5%</t>
+          <t>1-1:12.5% / 1-0:11.5% / 2-1:8.8%</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V94">
-        <v>57.62</v>
+        <v>16.66</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -9973,14 +9973,14 @@
         </is>
       </c>
       <c r="X94">
-        <v>-0.0534</v>
+        <v>-0.1143</v>
       </c>
       <c r="Y94">
         <v>0</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>周六018</t>
+          <t>周六022</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>马洛卡 对 奥维耶多</t>
+          <t>塞尔塔 对 塞维利亚</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10051,35 +10051,35 @@
         </is>
       </c>
       <c r="K95">
-        <v>0.6344</v>
+        <v>0.5438</v>
       </c>
       <c r="L95">
-        <v>0.2207</v>
+        <v>0.2578</v>
       </c>
       <c r="M95">
-        <v>0.1449</v>
+        <v>0.1984</v>
       </c>
       <c r="N95">
-        <v>0.6344</v>
+        <v>0.5438</v>
       </c>
       <c r="O95">
-        <v>0.2207</v>
+        <v>0.2578</v>
       </c>
       <c r="P95">
-        <v>0.1449</v>
+        <v>0.1984</v>
       </c>
       <c r="Q95">
-        <v>0.7056</v>
+        <v>0.7044</v>
       </c>
       <c r="R95">
-        <v>0.1837</v>
+        <v>0.1873</v>
       </c>
       <c r="S95">
-        <v>0.1108</v>
+        <v>0.1083</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>2-0:13% / 1-0:11.6% / 3-0:9.7%</t>
+          <t>2-0:13.4% / 1-0:12.5% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="V95">
-        <v>75.91</v>
+        <v>57.89</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="X95">
-        <v>-0.07</v>
+        <v>-0.0538</v>
       </c>
       <c r="Y95">
         <v>0</v>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>周六019</t>
+          <t>周六023</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>西班牙人 对 皇家社会</t>
+          <t>阿拉维斯 对 巴列卡诺</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10170,39 +10170,39 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K96">
-        <v>0.4214</v>
+        <v>0.3917</v>
       </c>
       <c r="L96">
-        <v>0.2855</v>
+        <v>0.3052</v>
       </c>
       <c r="M96">
-        <v>0.2931</v>
+        <v>0.3031</v>
       </c>
       <c r="N96">
-        <v>0.4214</v>
+        <v>0.3917</v>
       </c>
       <c r="O96">
-        <v>0.2855</v>
+        <v>0.3052</v>
       </c>
       <c r="P96">
-        <v>0.2931</v>
+        <v>0.3031</v>
       </c>
       <c r="Q96">
-        <v>0.4908</v>
+        <v>0.4522</v>
       </c>
       <c r="R96">
-        <v>0.25</v>
+        <v>0.2582</v>
       </c>
       <c r="S96">
-        <v>0.2592</v>
+        <v>0.2897</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1-1:12.1% / 1-0:10.9% / 2-1:9.3%</t>
+          <t>1-1:12.3% / 1-0:10.7% / 2-1:8.9%</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="V96">
-        <v>33.14</v>
+        <v>27.24</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -10219,14 +10219,14 @@
         </is>
       </c>
       <c r="X96">
-        <v>-0.1151</v>
+        <v>-0.1148</v>
       </c>
       <c r="Y96">
         <v>0</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>周六020</t>
+          <t>周六024</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10263,69 +10263,69 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>皇马 对 毕尔巴鄂</t>
+          <t>巴伦西亚 对 巴萨</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="K97">
-        <v>0.6459</v>
+        <v>0.2639</v>
       </c>
       <c r="L97">
-        <v>0.1991</v>
+        <v>0.2353</v>
       </c>
       <c r="M97">
-        <v>0.155</v>
+        <v>0.5008</v>
       </c>
       <c r="N97">
-        <v>0.6459</v>
+        <v>0.2639</v>
       </c>
       <c r="O97">
-        <v>0.1991</v>
+        <v>0.2353</v>
       </c>
       <c r="P97">
-        <v>0.155</v>
+        <v>0.5008</v>
       </c>
       <c r="Q97">
-        <v>0.7118</v>
+        <v>0.175</v>
       </c>
       <c r="R97">
-        <v>0.1812</v>
+        <v>0.2191</v>
       </c>
       <c r="S97">
-        <v>0.1071</v>
+        <v>0.606</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>2-0:13.1% / 1-0:12% / 3-0:9.4%</t>
+          <t>0-1:11.7% / 0-2:10.8% / 1-1:10.3%</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="V97">
-        <v>79.72</v>
+        <v>50.38</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -10342,14 +10342,14 @@
         </is>
       </c>
       <c r="X97">
-        <v>-0.0731</v>
+        <v>-0.073</v>
       </c>
       <c r="Y97">
         <v>0</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>周六021</t>
+          <t>周六025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>赫塔费 对 奥萨苏纳</t>
+          <t>贝蒂斯 对 莱万特</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10416,48 +10416,48 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="K98">
-        <v>0.3719</v>
+        <v>0.416</v>
       </c>
       <c r="L98">
-        <v>0.3471</v>
+        <v>0.2888</v>
       </c>
       <c r="M98">
-        <v>0.281</v>
+        <v>0.2951</v>
       </c>
       <c r="N98">
-        <v>0.3719</v>
+        <v>0.416</v>
       </c>
       <c r="O98">
-        <v>0.3471</v>
+        <v>0.2888</v>
       </c>
       <c r="P98">
-        <v>0.281</v>
+        <v>0.2951</v>
       </c>
       <c r="Q98">
-        <v>0.4535</v>
+        <v>0.4813</v>
       </c>
       <c r="R98">
-        <v>0.2616</v>
+        <v>0.2548</v>
       </c>
       <c r="S98">
-        <v>0.285</v>
+        <v>0.264</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1-1:12.5% / 1-0:11.5% / 2-1:9%</t>
+          <t>1-1:12.1% / 1-0:10.9% / 2-1:9.3%</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V98">
-        <v>18.51</v>
+        <v>33.83</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -10465,14 +10465,14 @@
         </is>
       </c>
       <c r="X98">
-        <v>-0.1149</v>
+        <v>-0.0557</v>
       </c>
       <c r="Y98">
         <v>0</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10499,17 +10499,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>周六022</t>
+          <t>周六026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>塞尔塔 对 塞维利亚</t>
+          <t>明尼苏达 对 盐湖城</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10539,39 +10539,39 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K99">
-        <v>0.5438</v>
+        <v>0.4291</v>
       </c>
       <c r="L99">
-        <v>0.2578</v>
+        <v>0.2591</v>
       </c>
       <c r="M99">
-        <v>0.1984</v>
+        <v>0.3118</v>
       </c>
       <c r="N99">
-        <v>0.5438</v>
+        <v>0.4291</v>
       </c>
       <c r="O99">
-        <v>0.2578</v>
+        <v>0.2591</v>
       </c>
       <c r="P99">
-        <v>0.1984</v>
+        <v>0.3118</v>
       </c>
       <c r="Q99">
-        <v>0.7044</v>
+        <v>0.4828</v>
       </c>
       <c r="R99">
-        <v>0.1873</v>
+        <v>0.2442</v>
       </c>
       <c r="S99">
-        <v>0.1083</v>
+        <v>0.273</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>2-0:13.4% / 1-0:12.5% / 2-1:9.6%</t>
+          <t>1-1:11.7% / 1-0:10.8% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="V99">
-        <v>57.89</v>
+        <v>34.45</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -10588,14 +10588,14 @@
         </is>
       </c>
       <c r="X99">
-        <v>-0.0538</v>
+        <v>-0.0813</v>
       </c>
       <c r="Y99">
         <v>0</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10622,17 +10622,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>周六023</t>
+          <t>周六027</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>阿拉维斯 对 巴列卡诺</t>
+          <t>夏洛特FC 对 新英格兰</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10662,48 +10662,48 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K100">
-        <v>0.3853</v>
+        <v>0.4926</v>
       </c>
       <c r="L100">
-        <v>0.3004</v>
+        <v>0.2556</v>
       </c>
       <c r="M100">
-        <v>0.3143</v>
+        <v>0.2518</v>
       </c>
       <c r="N100">
-        <v>0.3853</v>
+        <v>0.4926</v>
       </c>
       <c r="O100">
-        <v>0.3004</v>
+        <v>0.2556</v>
       </c>
       <c r="P100">
-        <v>0.3143</v>
+        <v>0.2518</v>
       </c>
       <c r="Q100">
-        <v>0.4329</v>
+        <v>0.6088</v>
       </c>
       <c r="R100">
-        <v>0.2588</v>
+        <v>0.2245</v>
       </c>
       <c r="S100">
-        <v>0.3084</v>
+        <v>0.1667</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1-1:12.4% / 1-0:10.4% / 2-1:8.8%</t>
+          <t>1-0:12.4% / 1-1:10.8% / 2-0:10.6%</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V100">
-        <v>23.63</v>
+        <v>49.8</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -10711,14 +10711,14 @@
         </is>
       </c>
       <c r="X100">
-        <v>-0.1138</v>
+        <v>-0.0813</v>
       </c>
       <c r="Y100">
         <v>0</v>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10745,79 +10745,79 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>周六024</t>
+          <t>周六028</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>巴伦西亚 对 巴萨</t>
+          <t>华盛顿 对 蒙特利尔</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K101">
-        <v>0.2639</v>
+        <v>0.4848</v>
       </c>
       <c r="L101">
-        <v>0.2353</v>
+        <v>0.2592</v>
       </c>
       <c r="M101">
-        <v>0.5008</v>
+        <v>0.256</v>
       </c>
       <c r="N101">
-        <v>0.2639</v>
+        <v>0.4848</v>
       </c>
       <c r="O101">
-        <v>0.2353</v>
+        <v>0.2592</v>
       </c>
       <c r="P101">
-        <v>0.5008</v>
+        <v>0.256</v>
       </c>
       <c r="Q101">
-        <v>0.175</v>
+        <v>0.5995</v>
       </c>
       <c r="R101">
-        <v>0.2191</v>
+        <v>0.2227</v>
       </c>
       <c r="S101">
-        <v>0.606</v>
+        <v>0.1779</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>0-1:11.7% / 0-2:10.8% / 1-1:10.3%</t>
+          <t>1-0:11.7% / 2-0:11% / 1-1:10.6%</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -10826,7 +10826,7 @@
         </is>
       </c>
       <c r="V101">
-        <v>50.38</v>
+        <v>48.21</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -10834,14 +10834,14 @@
         </is>
       </c>
       <c r="X101">
-        <v>-0.073</v>
+        <v>-0.0803</v>
       </c>
       <c r="Y101">
         <v>0</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10868,17 +10868,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>周六025</t>
+          <t>周六029</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>贝蒂斯 对 莱万特</t>
+          <t>纳什维尔 对 纽约城</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -10908,39 +10908,39 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K102">
-        <v>0.416</v>
+        <v>0.557</v>
       </c>
       <c r="L102">
-        <v>0.2888</v>
+        <v>0.2426</v>
       </c>
       <c r="M102">
-        <v>0.2951</v>
+        <v>0.2004</v>
       </c>
       <c r="N102">
-        <v>0.416</v>
+        <v>0.557</v>
       </c>
       <c r="O102">
-        <v>0.2888</v>
+        <v>0.2426</v>
       </c>
       <c r="P102">
-        <v>0.2951</v>
+        <v>0.2004</v>
       </c>
       <c r="Q102">
-        <v>0.4813</v>
+        <v>0.7061</v>
       </c>
       <c r="R102">
-        <v>0.2548</v>
+        <v>0.185</v>
       </c>
       <c r="S102">
-        <v>0.264</v>
+        <v>0.109</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1-1:12.1% / 1-0:10.9% / 2-1:9.3%</t>
+          <t>2-0:13.5% / 1-0:12.2% / 2-1:9.3%</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="V102">
-        <v>33.83</v>
+        <v>59.65</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -10957,14 +10957,14 @@
         </is>
       </c>
       <c r="X102">
-        <v>-0.0557</v>
+        <v>-0.1144</v>
       </c>
       <c r="Y102">
         <v>0</v>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>周六026</t>
+          <t>周六030</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>明尼苏达 对 盐湖城</t>
+          <t>波特兰 对 圣何塞</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11035,44 +11035,44 @@
         </is>
       </c>
       <c r="K103">
-        <v>0.4291</v>
+        <v>0.3987</v>
       </c>
       <c r="L103">
-        <v>0.2591</v>
+        <v>0.2408</v>
       </c>
       <c r="M103">
-        <v>0.3118</v>
+        <v>0.3605</v>
       </c>
       <c r="N103">
-        <v>0.4291</v>
+        <v>0.3987</v>
       </c>
       <c r="O103">
-        <v>0.2591</v>
+        <v>0.2408</v>
       </c>
       <c r="P103">
-        <v>0.3118</v>
+        <v>0.3605</v>
       </c>
       <c r="Q103">
-        <v>0.4828</v>
+        <v>0.4109</v>
       </c>
       <c r="R103">
-        <v>0.2442</v>
+        <v>0.2562</v>
       </c>
       <c r="S103">
-        <v>0.273</v>
+        <v>0.333</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1-1:11.7% / 1-0:10.8% / 2-1:9.6%</t>
+          <t>1-1:12.2% / 1-0:10% / 2-1:9%</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V103">
-        <v>34.45</v>
+        <v>23.39</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
@@ -11080,14 +11080,14 @@
         </is>
       </c>
       <c r="X103">
-        <v>-0.0813</v>
+        <v>-0.079</v>
       </c>
       <c r="Y103">
         <v>0</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11114,17 +11114,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>周六027</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>夏洛特FC 对 新英格兰</t>
+          <t>赫尔城 对 南安普敦</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11158,35 +11158,35 @@
         </is>
       </c>
       <c r="K104">
-        <v>0.4926</v>
+        <v>0.6828</v>
       </c>
       <c r="L104">
-        <v>0.2556</v>
+        <v>0.1762</v>
       </c>
       <c r="M104">
-        <v>0.2518</v>
+        <v>0.141</v>
       </c>
       <c r="N104">
-        <v>0.4926</v>
+        <v>0.6828</v>
       </c>
       <c r="O104">
-        <v>0.2556</v>
+        <v>0.1762</v>
       </c>
       <c r="P104">
-        <v>0.2518</v>
+        <v>0.141</v>
       </c>
       <c r="Q104">
-        <v>0.6088</v>
+        <v>0.7109</v>
       </c>
       <c r="R104">
-        <v>0.2245</v>
+        <v>0.1796</v>
       </c>
       <c r="S104">
-        <v>0.1667</v>
+        <v>0.1096</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1-0:12.4% / 1-1:10.8% / 2-0:10.6%</t>
+          <t>2-0:12.9% / 1-0:11.7% / 3-0:9.4%</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="V104">
-        <v>49.8</v>
+        <v>84.96</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -11203,14 +11203,14 @@
         </is>
       </c>
       <c r="X104">
-        <v>-0.0813</v>
+        <v>-0.0741</v>
       </c>
       <c r="Y104">
         <v>0</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：英冠，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11237,17 +11237,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>周六028</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>德国杯</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>华盛顿 对 蒙特利尔</t>
+          <t>拜仁慕尼黑 对 斯图加特</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11281,35 +11281,35 @@
         </is>
       </c>
       <c r="K105">
-        <v>0.4848</v>
+        <v>0.7045</v>
       </c>
       <c r="L105">
-        <v>0.2592</v>
+        <v>0.1655</v>
       </c>
       <c r="M105">
-        <v>0.256</v>
+        <v>0.13</v>
       </c>
       <c r="N105">
-        <v>0.4848</v>
+        <v>0.2543</v>
       </c>
       <c r="O105">
-        <v>0.2592</v>
+        <v>0.2447</v>
       </c>
       <c r="P105">
-        <v>0.256</v>
+        <v>0.501</v>
       </c>
       <c r="Q105">
-        <v>0.5995</v>
+        <v>0.1602</v>
       </c>
       <c r="R105">
-        <v>0.2227</v>
+        <v>0.2225</v>
       </c>
       <c r="S105">
-        <v>0.1779</v>
+        <v>0.6174</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1-0:11.7% / 2-0:11% / 1-1:10.6%</t>
+          <t>0-1:11.6% / 0-2:11.4% / 1-1:10.8%</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="V105">
-        <v>48.21</v>
+        <v>92.23</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -11326,14 +11326,14 @@
         </is>
       </c>
       <c r="X105">
-        <v>-0.0803</v>
+        <v>-0.0566</v>
       </c>
       <c r="Y105">
         <v>0</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11360,79 +11360,79 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>周六029</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>纳什维尔 对 纽约城</t>
+          <t>博洛尼亚 对 国际米兰</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="K106">
-        <v>0.557</v>
+        <v>0.2785</v>
       </c>
       <c r="L106">
-        <v>0.2426</v>
+        <v>0.253</v>
       </c>
       <c r="M106">
-        <v>0.2004</v>
+        <v>0.4685</v>
       </c>
       <c r="N106">
-        <v>0.557</v>
+        <v>0.627</v>
       </c>
       <c r="O106">
-        <v>0.2426</v>
+        <v>0.2197</v>
       </c>
       <c r="P106">
-        <v>0.2004</v>
+        <v>0.1532</v>
       </c>
       <c r="Q106">
-        <v>0.7061</v>
+        <v>0.7036</v>
       </c>
       <c r="R106">
-        <v>0.185</v>
+        <v>0.188</v>
       </c>
       <c r="S106">
-        <v>0.109</v>
+        <v>0.1084</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:12.2% / 2-1:9.3%</t>
+          <t>2-0:13.3% / 1-0:11.9% / 3-0:9.6%</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="V106">
-        <v>59.65</v>
+        <v>42.08</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -11449,14 +11449,14 @@
         </is>
       </c>
       <c r="X106">
-        <v>-0.1144</v>
+        <v>-0.0651</v>
       </c>
       <c r="Y106">
         <v>0</v>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11483,17 +11483,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>周六030</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>波特兰 对 圣何塞</t>
+          <t>拉齐奥 对 比萨</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11503,17 +11503,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -11523,48 +11523,48 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K107">
-        <v>0.3987</v>
+        <v>0.6014</v>
       </c>
       <c r="L107">
-        <v>0.2408</v>
+        <v>0.2297</v>
       </c>
       <c r="M107">
-        <v>0.3605</v>
+        <v>0.1689</v>
       </c>
       <c r="N107">
-        <v>0.3987</v>
+        <v>0.4947</v>
       </c>
       <c r="O107">
-        <v>0.2408</v>
+        <v>0.2664</v>
       </c>
       <c r="P107">
-        <v>0.3605</v>
+        <v>0.239</v>
       </c>
       <c r="Q107">
-        <v>0.4109</v>
+        <v>0.6228</v>
       </c>
       <c r="R107">
-        <v>0.2562</v>
+        <v>0.2126</v>
       </c>
       <c r="S107">
-        <v>0.333</v>
+        <v>0.1647</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:10% / 2-1:9%</t>
+          <t>1-0:11.9% / 2-0:11.6% / 1-1:9.9%</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V107">
-        <v>23.39</v>
+        <v>69.75</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>
@@ -11572,14 +11572,14 @@
         </is>
       </c>
       <c r="X107">
-        <v>-0.079</v>
+        <v>-0.065</v>
       </c>
       <c r="Y107">
         <v>0</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11606,17 +11606,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>赫尔城 对 南安普敦</t>
+          <t>维戈塞尔塔 对 塞维利亚</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -11650,35 +11650,35 @@
         </is>
       </c>
       <c r="K108">
-        <v>0.6828</v>
+        <v>0.5438</v>
       </c>
       <c r="L108">
-        <v>0.1762</v>
+        <v>0.2578</v>
       </c>
       <c r="M108">
-        <v>0.141</v>
+        <v>0.1984</v>
       </c>
       <c r="N108">
-        <v>0.6828</v>
+        <v>0.3949</v>
       </c>
       <c r="O108">
-        <v>0.1762</v>
+        <v>0.3331</v>
       </c>
       <c r="P108">
-        <v>0.141</v>
+        <v>0.272</v>
       </c>
       <c r="Q108">
-        <v>0.7109</v>
+        <v>0.482</v>
       </c>
       <c r="R108">
-        <v>0.1796</v>
+        <v>0.2551</v>
       </c>
       <c r="S108">
-        <v>0.1096</v>
+        <v>0.2629</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>2-0:12.9% / 1-0:11.7% / 3-0:9.4%</t>
+          <t>1-1:12.2% / 1-0:11.4% / 2-1:9.4%</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -11687,7 +11687,7 @@
         </is>
       </c>
       <c r="V108">
-        <v>84.96</v>
+        <v>57.89</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -11695,14 +11695,14 @@
         </is>
       </c>
       <c r="X108">
-        <v>-0.0741</v>
+        <v>-0.0645</v>
       </c>
       <c r="Y108">
         <v>0</v>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>经模型综合分析：英冠，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11729,17 +11729,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>德国杯</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>拜仁慕尼黑 对 斯图加特</t>
+          <t>赫塔费 对 奥萨苏纳</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11754,17 +11754,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -11773,44 +11773,44 @@
         </is>
       </c>
       <c r="K109">
-        <v>0.7045</v>
+        <v>0.3645</v>
       </c>
       <c r="L109">
-        <v>0.1655</v>
+        <v>0.3543</v>
       </c>
       <c r="M109">
-        <v>0.13</v>
+        <v>0.2812</v>
       </c>
       <c r="N109">
-        <v>0.2543</v>
+        <v>0.5101</v>
       </c>
       <c r="O109">
-        <v>0.2447</v>
+        <v>0.2496</v>
       </c>
       <c r="P109">
-        <v>0.501</v>
+        <v>0.2402</v>
       </c>
       <c r="Q109">
-        <v>0.1602</v>
+        <v>0.6407</v>
       </c>
       <c r="R109">
-        <v>0.2225</v>
+        <v>0.2083</v>
       </c>
       <c r="S109">
-        <v>0.6174</v>
+        <v>0.1511</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>0-1:11.6% / 0-2:11.4% / 1-1:10.8%</t>
+          <t>1-0:12.4% / 2-0:12% / 1-1:10.1%</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V109">
-        <v>92.23</v>
+        <v>16.66</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11818,14 +11818,14 @@
         </is>
       </c>
       <c r="X109">
-        <v>-0.0566</v>
+        <v>-0.066</v>
       </c>
       <c r="Y109">
         <v>0</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11852,79 +11852,79 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>博洛尼亚 对 国际米兰</t>
+          <t>赫罗纳 对 埃尔切</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-主胜</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K110">
-        <v>0.2785</v>
+        <v>0.5348</v>
       </c>
       <c r="L110">
-        <v>0.253</v>
+        <v>0.2446</v>
       </c>
       <c r="M110">
-        <v>0.4685</v>
+        <v>0.2206</v>
       </c>
       <c r="N110">
-        <v>0.627</v>
+        <v>0.4605</v>
       </c>
       <c r="O110">
-        <v>0.2197</v>
+        <v>0.2536</v>
       </c>
       <c r="P110">
-        <v>0.1532</v>
+        <v>0.2859</v>
       </c>
       <c r="Q110">
-        <v>0.7036</v>
+        <v>0.5475</v>
       </c>
       <c r="R110">
-        <v>0.188</v>
+        <v>0.2369</v>
       </c>
       <c r="S110">
-        <v>0.1084</v>
+        <v>0.2157</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>2-0:13.3% / 1-0:11.9% / 3-0:9.6%</t>
+          <t>1-0:11.4% / 1-1:11% / 2-1:9.9%</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -11933,7 +11933,7 @@
         </is>
       </c>
       <c r="V110">
-        <v>42.08</v>
+        <v>57.62</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -11941,14 +11941,14 @@
         </is>
       </c>
       <c r="X110">
-        <v>-0.0651</v>
+        <v>-0.0606</v>
       </c>
       <c r="Y110">
         <v>0</v>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11975,17 +11975,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>荷乙</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>拉齐奥 对 比萨</t>
+          <t>福伦丹 对 威廉二世</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11995,17 +11995,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -12015,39 +12015,39 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K111">
-        <v>0.6014</v>
+        <v>0.4352</v>
       </c>
       <c r="L111">
-        <v>0.2297</v>
+        <v>0.2643</v>
       </c>
       <c r="M111">
-        <v>0.1689</v>
+        <v>0.3005</v>
       </c>
       <c r="N111">
-        <v>0.4947</v>
+        <v>0.3999</v>
       </c>
       <c r="O111">
-        <v>0.2664</v>
+        <v>0.2717</v>
       </c>
       <c r="P111">
-        <v>0.239</v>
+        <v>0.3284</v>
       </c>
       <c r="Q111">
-        <v>0.6228</v>
+        <v>0.44</v>
       </c>
       <c r="R111">
-        <v>0.2126</v>
+        <v>0.2542</v>
       </c>
       <c r="S111">
-        <v>0.1647</v>
+        <v>0.3059</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1-0:11.9% / 2-0:11.6% / 1-1:9.9%</t>
+          <t>1-1:11.9% / 1-0:10.1% / 2-1:9.2%</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="V111">
-        <v>69.75</v>
+        <v>36.46</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -12064,14 +12064,14 @@
         </is>
       </c>
       <c r="X111">
-        <v>-0.065</v>
+        <v>-0.079</v>
       </c>
       <c r="Y111">
         <v>0</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12098,17 +12098,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>维戈塞尔塔 对 塞维利亚</t>
+          <t>哈尔姆斯塔德 对 厄尔格里特</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -12138,39 +12138,39 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>主胜-客胜</t>
         </is>
       </c>
       <c r="K112">
-        <v>0.5438</v>
+        <v>0.4354</v>
       </c>
       <c r="L112">
-        <v>0.2578</v>
+        <v>0.2737</v>
       </c>
       <c r="M112">
-        <v>0.1984</v>
+        <v>0.291</v>
       </c>
       <c r="N112">
-        <v>0.3949</v>
+        <v>0.4354</v>
       </c>
       <c r="O112">
-        <v>0.3331</v>
+        <v>0.2737</v>
       </c>
       <c r="P112">
-        <v>0.272</v>
+        <v>0.291</v>
       </c>
       <c r="Q112">
-        <v>0.482</v>
+        <v>0.511</v>
       </c>
       <c r="R112">
-        <v>0.2551</v>
+        <v>0.2464</v>
       </c>
       <c r="S112">
-        <v>0.2629</v>
+        <v>0.2427</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:11.4% / 2-1:9.4%</t>
+          <t>1-1:12% / 1-0:11.3% / 2-1:9.2%</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="V112">
-        <v>57.89</v>
+        <v>34.54</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -12187,14 +12187,14 @@
         </is>
       </c>
       <c r="X112">
-        <v>-0.0645</v>
+        <v>-0.0804</v>
       </c>
       <c r="Y112">
         <v>0</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12221,17 +12221,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>赫塔费 对 奥萨苏纳</t>
+          <t>卡尔马 对 代格福什</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12265,44 +12265,44 @@
         </is>
       </c>
       <c r="K113">
-        <v>0.3719</v>
+        <v>0.4872</v>
       </c>
       <c r="L113">
-        <v>0.3471</v>
+        <v>0.2814</v>
       </c>
       <c r="M113">
-        <v>0.281</v>
+        <v>0.2314</v>
       </c>
       <c r="N113">
-        <v>0.5101</v>
+        <v>0.4445</v>
       </c>
       <c r="O113">
-        <v>0.2496</v>
+        <v>0.291</v>
       </c>
       <c r="P113">
-        <v>0.2402</v>
+        <v>0.2645</v>
       </c>
       <c r="Q113">
-        <v>0.6407</v>
+        <v>0.5478</v>
       </c>
       <c r="R113">
-        <v>0.2083</v>
+        <v>0.2373</v>
       </c>
       <c r="S113">
-        <v>0.1511</v>
+        <v>0.2149</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1-0:12.4% / 2-0:12% / 1-1:10.1%</t>
+          <t>1-1:11.3% / 1-0:11.3% / 2-0:10.3%</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V113">
-        <v>18.51</v>
+        <v>46.6</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -12310,14 +12310,14 @@
         </is>
       </c>
       <c r="X113">
-        <v>-0.066</v>
+        <v>-0.0812</v>
       </c>
       <c r="Y113">
         <v>0</v>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12344,17 +12344,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>赫罗纳 对 埃尔切</t>
+          <t>坦佩雷山猫 对 赫尔辛基火花</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -12384,39 +12384,39 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K114">
-        <v>0.5348</v>
+        <v>0.5009</v>
       </c>
       <c r="L114">
-        <v>0.2446</v>
+        <v>0.2465</v>
       </c>
       <c r="M114">
-        <v>0.2206</v>
+        <v>0.2526</v>
       </c>
       <c r="N114">
-        <v>0.4605</v>
+        <v>0.521</v>
       </c>
       <c r="O114">
-        <v>0.2536</v>
+        <v>0.2408</v>
       </c>
       <c r="P114">
-        <v>0.2859</v>
+        <v>0.2382</v>
       </c>
       <c r="Q114">
-        <v>0.5475</v>
+        <v>0.6562</v>
       </c>
       <c r="R114">
-        <v>0.2369</v>
+        <v>0.2042</v>
       </c>
       <c r="S114">
-        <v>0.2157</v>
+        <v>0.1396</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1-0:11.4% / 1-1:11% / 2-1:9.9%</t>
+          <t>1-0:12.4% / 2-0:11.8% / 1-1:10.2%</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="V114">
-        <v>57.62</v>
+        <v>51.41</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -12433,14 +12433,14 @@
         </is>
       </c>
       <c r="X114">
-        <v>-0.0606</v>
+        <v>-0.0737</v>
       </c>
       <c r="Y114">
         <v>0</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12467,17 +12467,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>福伦丹 对 威廉二世</t>
+          <t>雅罗 对 玛丽港</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -12507,39 +12507,39 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K115">
-        <v>0.4352</v>
+        <v>0.4828</v>
       </c>
       <c r="L115">
-        <v>0.2643</v>
+        <v>0.272</v>
       </c>
       <c r="M115">
-        <v>0.3005</v>
+        <v>0.2452</v>
       </c>
       <c r="N115">
-        <v>0.3999</v>
+        <v>0.4923</v>
       </c>
       <c r="O115">
-        <v>0.2717</v>
+        <v>0.2635</v>
       </c>
       <c r="P115">
-        <v>0.3284</v>
+        <v>0.2441</v>
       </c>
       <c r="Q115">
-        <v>0.44</v>
+        <v>0.615</v>
       </c>
       <c r="R115">
-        <v>0.2542</v>
+        <v>0.2164</v>
       </c>
       <c r="S115">
-        <v>0.3059</v>
+        <v>0.1687</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1-1:11.9% / 1-0:10.1% / 2-1:9.2%</t>
+          <t>1-0:12.1% / 2-0:11.7% / 1-1:10%</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -12548,7 +12548,7 @@
         </is>
       </c>
       <c r="V115">
-        <v>36.46</v>
+        <v>46.73</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -12556,14 +12556,14 @@
         </is>
       </c>
       <c r="X115">
-        <v>-0.079</v>
+        <v>-0.0814</v>
       </c>
       <c r="Y115">
         <v>0</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12590,17 +12590,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>哈尔姆斯塔德 对 厄尔格里特</t>
+          <t>库奥皮奥 对 拉赫蒂</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -12610,17 +12610,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -12630,39 +12630,39 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K116">
-        <v>0.4354</v>
+        <v>0.5934</v>
       </c>
       <c r="L116">
-        <v>0.2737</v>
+        <v>0.2361</v>
       </c>
       <c r="M116">
-        <v>0.291</v>
+        <v>0.1705</v>
       </c>
       <c r="N116">
-        <v>0.4354</v>
+        <v>0.5759</v>
       </c>
       <c r="O116">
-        <v>0.2737</v>
+        <v>0.2432</v>
       </c>
       <c r="P116">
-        <v>0.291</v>
+        <v>0.181</v>
       </c>
       <c r="Q116">
-        <v>0.511</v>
+        <v>0.7019</v>
       </c>
       <c r="R116">
-        <v>0.2464</v>
+        <v>0.1851</v>
       </c>
       <c r="S116">
-        <v>0.2427</v>
+        <v>0.113</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1-1:12% / 1-0:11.3% / 2-1:9.2%</t>
+          <t>2-0:12.6% / 1-0:12.5% / 3-0:9.6%</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -12671,7 +12671,7 @@
         </is>
       </c>
       <c r="V116">
-        <v>34.54</v>
+        <v>67.88</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
@@ -12679,14 +12679,14 @@
         </is>
       </c>
       <c r="X116">
-        <v>-0.0804</v>
+        <v>-0.0837</v>
       </c>
       <c r="Y116">
         <v>0</v>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12713,17 +12713,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>卡尔马 对 代格福什</t>
+          <t>塞伊奈约基 对 AC 奥卢</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -12753,48 +12753,48 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K117">
-        <v>0.4872</v>
+        <v>0.3731</v>
       </c>
       <c r="L117">
-        <v>0.2814</v>
+        <v>0.2676</v>
       </c>
       <c r="M117">
-        <v>0.2314</v>
+        <v>0.3593</v>
       </c>
       <c r="N117">
-        <v>0.443</v>
+        <v>0.369</v>
       </c>
       <c r="O117">
-        <v>0.2916</v>
+        <v>0.2689</v>
       </c>
       <c r="P117">
-        <v>0.2655</v>
+        <v>0.362</v>
       </c>
       <c r="Q117">
-        <v>0.5469</v>
+        <v>0.3796</v>
       </c>
       <c r="R117">
-        <v>0.2359</v>
+        <v>0.2597</v>
       </c>
       <c r="S117">
-        <v>0.2172</v>
+        <v>0.3607</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>1-0:11.4% / 1-1:11.3% / 2-0:10.3%</t>
+          <t>1-1:12.4% / 1-0:9.5% / 0-1:9.2%</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V117">
-        <v>46.6</v>
+        <v>19.36</v>
       </c>
       <c r="W117" t="inlineStr">
         <is>
@@ -12802,14 +12802,14 @@
         </is>
       </c>
       <c r="X117">
-        <v>-0.0821</v>
+        <v>-0.0834</v>
       </c>
       <c r="Y117">
         <v>0</v>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12823,504 +12823,12 @@
         </is>
       </c>
       <c r="AC117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>坦佩雷山猫 对 赫尔辛基火花</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>平局-主胜</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>主胜-客胜</t>
-        </is>
-      </c>
-      <c r="K118">
-        <v>0.5009</v>
-      </c>
-      <c r="L118">
-        <v>0.2465</v>
-      </c>
-      <c r="M118">
-        <v>0.2526</v>
-      </c>
-      <c r="N118">
-        <v>0.521</v>
-      </c>
-      <c r="O118">
-        <v>0.2408</v>
-      </c>
-      <c r="P118">
-        <v>0.2382</v>
-      </c>
-      <c r="Q118">
-        <v>0.6562</v>
-      </c>
-      <c r="R118">
-        <v>0.2042</v>
-      </c>
-      <c r="S118">
-        <v>0.1396</v>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>1-0:12.4% / 2-0:11.8% / 1-1:10.2%</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="V118">
-        <v>51.41</v>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X118">
-        <v>-0.0737</v>
-      </c>
-      <c r="Y118">
-        <v>0</v>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>雅罗 对 玛丽港</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>客胜-主胜</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>平局-平局</t>
-        </is>
-      </c>
-      <c r="K119">
-        <v>0.4828</v>
-      </c>
-      <c r="L119">
-        <v>0.272</v>
-      </c>
-      <c r="M119">
-        <v>0.2452</v>
-      </c>
-      <c r="N119">
-        <v>0.4923</v>
-      </c>
-      <c r="O119">
-        <v>0.2635</v>
-      </c>
-      <c r="P119">
-        <v>0.2441</v>
-      </c>
-      <c r="Q119">
-        <v>0.615</v>
-      </c>
-      <c r="R119">
-        <v>0.2164</v>
-      </c>
-      <c r="S119">
-        <v>0.1687</v>
-      </c>
-      <c r="T119" t="inlineStr">
-        <is>
-          <t>1-0:12.1% / 2-0:11.7% / 1-1:10%</t>
-        </is>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="V119">
-        <v>46.73</v>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X119">
-        <v>-0.0814</v>
-      </c>
-      <c r="Y119">
-        <v>0</v>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>库奥皮奥 对 拉赫蒂</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>客胜-主胜</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>平局-平局</t>
-        </is>
-      </c>
-      <c r="K120">
-        <v>0.5934</v>
-      </c>
-      <c r="L120">
-        <v>0.2361</v>
-      </c>
-      <c r="M120">
-        <v>0.1705</v>
-      </c>
-      <c r="N120">
-        <v>0.5759</v>
-      </c>
-      <c r="O120">
-        <v>0.2432</v>
-      </c>
-      <c r="P120">
-        <v>0.181</v>
-      </c>
-      <c r="Q120">
-        <v>0.7019</v>
-      </c>
-      <c r="R120">
-        <v>0.1851</v>
-      </c>
-      <c r="S120">
-        <v>0.113</v>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>2-0:12.6% / 1-0:12.5% / 3-0:9.6%</t>
-        </is>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="V120">
-        <v>67.88</v>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X120">
-        <v>-0.0837</v>
-      </c>
-      <c r="Y120">
-        <v>0</v>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>塞伊奈约基 对 AC 奥卢</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>平局-主胜</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>主胜-客胜</t>
-        </is>
-      </c>
-      <c r="K121">
-        <v>0.3731</v>
-      </c>
-      <c r="L121">
-        <v>0.2676</v>
-      </c>
-      <c r="M121">
-        <v>0.3593</v>
-      </c>
-      <c r="N121">
-        <v>0.369</v>
-      </c>
-      <c r="O121">
-        <v>0.2689</v>
-      </c>
-      <c r="P121">
-        <v>0.362</v>
-      </c>
-      <c r="Q121">
-        <v>0.3796</v>
-      </c>
-      <c r="R121">
-        <v>0.2597</v>
-      </c>
-      <c r="S121">
-        <v>0.3607</v>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>1-1:12.4% / 1-0:9.5% / 0-1:9.2%</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="V121">
-        <v>19.36</v>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X121">
-        <v>-0.0834</v>
-      </c>
-      <c r="Y121">
-        <v>0</v>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD121"/>
+  <autoFilter ref="A1:AD117"/>
 </worksheet>
 </file>
--- a/data/exports/football-recap-master.xlsx
+++ b/data/exports/football-recap-master.xlsx
@@ -8197,7 +8197,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K82">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K86">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K88">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K97">
@@ -10411,12 +10411,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K98">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K103">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K106">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -12138,7 +12138,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>主胜-客胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K112">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>客胜-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">

--- a/data/exports/football-recap-master.xlsx
+++ b/data/exports/football-recap-master.xlsx
@@ -8039,17 +8039,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>周六006</t>
+          <t>周六008</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>哈尔姆斯 对 厄格里特</t>
+          <t>坦山猫 对 赫尔火花</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8079,39 +8079,39 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K79">
-        <v>0.454</v>
+        <v>0.5009</v>
       </c>
       <c r="L79">
-        <v>0.2856</v>
+        <v>0.2465</v>
       </c>
       <c r="M79">
-        <v>0.2604</v>
+        <v>0.2526</v>
       </c>
       <c r="N79">
-        <v>0.454</v>
+        <v>0.5009</v>
       </c>
       <c r="O79">
-        <v>0.2856</v>
+        <v>0.2465</v>
       </c>
       <c r="P79">
-        <v>0.2604</v>
+        <v>0.2526</v>
       </c>
       <c r="Q79">
-        <v>0.566</v>
+        <v>0.6198</v>
       </c>
       <c r="R79">
-        <v>0.2321</v>
+        <v>0.2187</v>
       </c>
       <c r="S79">
-        <v>0.202</v>
+        <v>0.1616</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1-0:11.8% / 1-1:11.3% / 2-0:10.5%</t>
+          <t>1-0:12.1% / 2-0:11.5% / 1-1:10.5%</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="V79">
-        <v>39.09</v>
+        <v>51.41</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -8128,14 +8128,14 @@
         </is>
       </c>
       <c r="X79">
-        <v>-0.1147</v>
+        <v>-0.0638</v>
       </c>
       <c r="Y79">
         <v>0</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8162,17 +8162,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>周六007</t>
+          <t>周六009</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>卡尔马 对 代格福什</t>
+          <t>塞伊奈 对 AC奥卢</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -8202,48 +8202,48 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K80">
-        <v>0.4872</v>
+        <v>0.3731</v>
       </c>
       <c r="L80">
-        <v>0.2814</v>
+        <v>0.2676</v>
       </c>
       <c r="M80">
-        <v>0.2314</v>
+        <v>0.3593</v>
       </c>
       <c r="N80">
-        <v>0.4872</v>
+        <v>0.3731</v>
       </c>
       <c r="O80">
-        <v>0.2814</v>
+        <v>0.2676</v>
       </c>
       <c r="P80">
-        <v>0.2314</v>
+        <v>0.3593</v>
       </c>
       <c r="Q80">
-        <v>0.6213</v>
+        <v>0.3832</v>
       </c>
       <c r="R80">
-        <v>0.2177</v>
+        <v>0.2598</v>
       </c>
       <c r="S80">
-        <v>0.1611</v>
+        <v>0.3571</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1-0:12.3% / 2-0:11.4% / 1-1:10.2%</t>
+          <t>1-1:12.6% / 1-0:10% / 0-1:9%</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V80">
-        <v>46.6</v>
+        <v>19.36</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -8251,14 +8251,14 @@
         </is>
       </c>
       <c r="X80">
-        <v>-0.0743</v>
+        <v>-0.0777</v>
       </c>
       <c r="Y80">
         <v>0</v>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>周六008</t>
+          <t>周六010</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>坦山猫 对 赫尔火花</t>
+          <t>库奥皮奥 对 拉赫蒂</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8305,17 +8305,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8325,39 +8325,39 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K81">
-        <v>0.5009</v>
+        <v>0.5934</v>
       </c>
       <c r="L81">
-        <v>0.2465</v>
+        <v>0.2361</v>
       </c>
       <c r="M81">
-        <v>0.2526</v>
+        <v>0.1705</v>
       </c>
       <c r="N81">
-        <v>0.5009</v>
+        <v>0.5934</v>
       </c>
       <c r="O81">
-        <v>0.2465</v>
+        <v>0.2361</v>
       </c>
       <c r="P81">
-        <v>0.2526</v>
+        <v>0.1705</v>
       </c>
       <c r="Q81">
-        <v>0.6198</v>
+        <v>0.7053</v>
       </c>
       <c r="R81">
-        <v>0.2187</v>
+        <v>0.1834</v>
       </c>
       <c r="S81">
-        <v>0.1616</v>
+        <v>0.1114</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1-0:12.1% / 2-0:11.5% / 1-1:10.5%</t>
+          <t>2-0:13.1% / 1-0:11.9% / 3-0:9.6%</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="V81">
-        <v>51.41</v>
+        <v>67.88</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8374,14 +8374,14 @@
         </is>
       </c>
       <c r="X81">
-        <v>-0.0638</v>
+        <v>-0.0743</v>
       </c>
       <c r="Y81">
         <v>0</v>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>周六009</t>
+          <t>周六011</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>塞伊奈 对 AC奥卢</t>
+          <t>雅罗 对 玛丽港</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8448,48 +8448,48 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K82">
-        <v>0.3731</v>
+        <v>0.4828</v>
       </c>
       <c r="L82">
-        <v>0.2676</v>
+        <v>0.272</v>
       </c>
       <c r="M82">
-        <v>0.3593</v>
+        <v>0.2452</v>
       </c>
       <c r="N82">
-        <v>0.3731</v>
+        <v>0.4828</v>
       </c>
       <c r="O82">
-        <v>0.2676</v>
+        <v>0.272</v>
       </c>
       <c r="P82">
-        <v>0.3593</v>
+        <v>0.2452</v>
       </c>
       <c r="Q82">
-        <v>0.3832</v>
+        <v>0.6085</v>
       </c>
       <c r="R82">
-        <v>0.2598</v>
+        <v>0.2202</v>
       </c>
       <c r="S82">
-        <v>0.3571</v>
+        <v>0.1714</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1-1:12.6% / 1-0:10% / 0-1:9%</t>
+          <t>1-0:11.7% / 2-0:11.1% / 1-1:10.5%</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V82">
-        <v>19.36</v>
+        <v>46.73</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8497,14 +8497,14 @@
         </is>
       </c>
       <c r="X82">
-        <v>-0.0777</v>
+        <v>-0.0779</v>
       </c>
       <c r="Y82">
         <v>0</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8531,22 +8531,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>周六010</t>
+          <t>周六012</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>库奥皮奥 对 拉赫蒂</t>
+          <t>赫尔城 对 米堡</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8556,17 +8556,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8575,35 +8575,35 @@
         </is>
       </c>
       <c r="K83">
-        <v>0.5934</v>
+        <v>0.2231</v>
       </c>
       <c r="L83">
-        <v>0.2361</v>
+        <v>0.2904</v>
       </c>
       <c r="M83">
-        <v>0.1705</v>
+        <v>0.4866</v>
       </c>
       <c r="N83">
-        <v>0.5934</v>
+        <v>0.2231</v>
       </c>
       <c r="O83">
-        <v>0.2361</v>
+        <v>0.2904</v>
       </c>
       <c r="P83">
-        <v>0.1705</v>
+        <v>0.4866</v>
       </c>
       <c r="Q83">
-        <v>0.7053</v>
+        <v>0.1558</v>
       </c>
       <c r="R83">
-        <v>0.1834</v>
+        <v>0.214</v>
       </c>
       <c r="S83">
-        <v>0.1114</v>
+        <v>0.6303</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>2-0:13.1% / 1-0:11.9% / 3-0:9.6%</t>
+          <t>0-1:12.3% / 0-2:11.9% / 1-2:10.1%</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="V83">
-        <v>67.88</v>
+        <v>43.94</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8620,14 +8620,14 @@
         </is>
       </c>
       <c r="X83">
-        <v>-0.0743</v>
+        <v>-0.1144</v>
       </c>
       <c r="Y83">
         <v>0</v>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：英冠，客胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8654,79 +8654,79 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>周六011</t>
+          <t>周六013</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>雅罗 对 玛丽港</t>
+          <t>博洛尼亚 对 国际米兰</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="K84">
-        <v>0.4828</v>
+        <v>0.2904</v>
       </c>
       <c r="L84">
-        <v>0.272</v>
+        <v>0.2531</v>
       </c>
       <c r="M84">
-        <v>0.2452</v>
+        <v>0.4565</v>
       </c>
       <c r="N84">
-        <v>0.4828</v>
+        <v>0.2904</v>
       </c>
       <c r="O84">
-        <v>0.272</v>
+        <v>0.2531</v>
       </c>
       <c r="P84">
-        <v>0.2452</v>
+        <v>0.4565</v>
       </c>
       <c r="Q84">
-        <v>0.6085</v>
+        <v>0.2243</v>
       </c>
       <c r="R84">
-        <v>0.2202</v>
+        <v>0.2405</v>
       </c>
       <c r="S84">
-        <v>0.1714</v>
+        <v>0.5353</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1-0:11.7% / 2-0:11.1% / 1-1:10.5%</t>
+          <t>1-1:11.5% / 0-1:10.9% / 1-2:10%</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="V84">
-        <v>46.73</v>
+        <v>39.07</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8743,14 +8743,14 @@
         </is>
       </c>
       <c r="X84">
-        <v>-0.0779</v>
+        <v>-0.1144</v>
       </c>
       <c r="Y84">
         <v>0</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -8777,22 +8777,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>周六012</t>
+          <t>周六014</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>德国杯</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>赫尔城 对 米堡</t>
+          <t>拜仁 对 斯图加特</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8802,54 +8802,54 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K85">
-        <v>0.2231</v>
+        <v>0.7045</v>
       </c>
       <c r="L85">
-        <v>0.2904</v>
+        <v>0.1655</v>
       </c>
       <c r="M85">
-        <v>0.4866</v>
+        <v>0.13</v>
       </c>
       <c r="N85">
-        <v>0.2231</v>
+        <v>0.7045</v>
       </c>
       <c r="O85">
-        <v>0.2904</v>
+        <v>0.1655</v>
       </c>
       <c r="P85">
-        <v>0.4866</v>
+        <v>0.13</v>
       </c>
       <c r="Q85">
-        <v>0.1558</v>
+        <v>0.711</v>
       </c>
       <c r="R85">
-        <v>0.214</v>
+        <v>0.1764</v>
       </c>
       <c r="S85">
-        <v>0.6303</v>
+        <v>0.1127</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>0-1:12.3% / 0-2:11.9% / 1-2:10.1%</t>
+          <t>2-0:12.6% / 1-0:11.1% / 2-1:9.7%</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="V85">
-        <v>43.94</v>
+        <v>92.23</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8866,14 +8866,14 @@
         </is>
       </c>
       <c r="X85">
-        <v>-0.1144</v>
+        <v>-0.063</v>
       </c>
       <c r="Y85">
         <v>0</v>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>经模型综合分析：英冠，客胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -8900,79 +8900,79 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>周六013</t>
+          <t>周六015</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>荷乙</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>博洛尼亚 对 国际米兰</t>
+          <t>福伦丹 对 威廉二世</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>主胜-主胜</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
           <t>客胜-客胜</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
       <c r="K86">
-        <v>0.2785</v>
+        <v>0.4352</v>
       </c>
       <c r="L86">
-        <v>0.253</v>
+        <v>0.2643</v>
       </c>
       <c r="M86">
-        <v>0.4685</v>
+        <v>0.3005</v>
       </c>
       <c r="N86">
-        <v>0.2785</v>
+        <v>0.4352</v>
       </c>
       <c r="O86">
-        <v>0.253</v>
+        <v>0.2643</v>
       </c>
       <c r="P86">
-        <v>0.4685</v>
+        <v>0.3005</v>
       </c>
       <c r="Q86">
-        <v>0.2088</v>
+        <v>0.504</v>
       </c>
       <c r="R86">
-        <v>0.2331</v>
+        <v>0.2456</v>
       </c>
       <c r="S86">
-        <v>0.5582</v>
+        <v>0.2504</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1-1:11.3% / 0-1:10.9% / 0-2:10.2%</t>
+          <t>1-1:11.7% / 1-0:10.9% / 2-1:9.8%</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="V86">
-        <v>42.08</v>
+        <v>36.46</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="X86">
-        <v>-0.1145</v>
+        <v>-0.0774</v>
       </c>
       <c r="Y86">
         <v>0</v>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9023,17 +9023,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>周六014</t>
+          <t>周六016</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>德国杯</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>拜仁 对 斯图加特</t>
+          <t>拉齐奥 对 比萨</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9067,35 +9067,35 @@
         </is>
       </c>
       <c r="K87">
-        <v>0.7045</v>
+        <v>0.6014</v>
       </c>
       <c r="L87">
-        <v>0.1655</v>
+        <v>0.2297</v>
       </c>
       <c r="M87">
-        <v>0.13</v>
+        <v>0.1689</v>
       </c>
       <c r="N87">
-        <v>0.7045</v>
+        <v>0.6014</v>
       </c>
       <c r="O87">
-        <v>0.1655</v>
+        <v>0.2297</v>
       </c>
       <c r="P87">
-        <v>0.13</v>
+        <v>0.1689</v>
       </c>
       <c r="Q87">
-        <v>0.711</v>
+        <v>0.7064</v>
       </c>
       <c r="R87">
-        <v>0.1764</v>
+        <v>0.1832</v>
       </c>
       <c r="S87">
-        <v>0.1127</v>
+        <v>0.1105</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2-0:12.6% / 1-0:11.1% / 2-1:9.7%</t>
+          <t>2-0:13.5% / 1-0:11.9% / 2-1:9.8%</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="V87">
-        <v>92.23</v>
+        <v>69.75</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
@@ -9112,14 +9112,14 @@
         </is>
       </c>
       <c r="X87">
-        <v>-0.063</v>
+        <v>-0.0558</v>
       </c>
       <c r="Y87">
         <v>0</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>周六015</t>
+          <t>周六017</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>福伦丹 对 威廉二世</t>
+          <t>赫罗纳 对 埃尔切</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9186,39 +9186,39 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K88">
-        <v>0.4352</v>
+        <v>0.5348</v>
       </c>
       <c r="L88">
-        <v>0.2643</v>
+        <v>0.2446</v>
       </c>
       <c r="M88">
-        <v>0.3005</v>
+        <v>0.2206</v>
       </c>
       <c r="N88">
-        <v>0.4352</v>
+        <v>0.5348</v>
       </c>
       <c r="O88">
-        <v>0.2643</v>
+        <v>0.2446</v>
       </c>
       <c r="P88">
-        <v>0.3005</v>
+        <v>0.2206</v>
       </c>
       <c r="Q88">
-        <v>0.504</v>
+        <v>0.6805</v>
       </c>
       <c r="R88">
-        <v>0.2456</v>
+        <v>0.1961</v>
       </c>
       <c r="S88">
-        <v>0.2504</v>
+        <v>0.1235</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1-1:11.7% / 1-0:10.9% / 2-1:9.8%</t>
+          <t>2-0:12.7% / 1-0:12.1% / 1-1:9.5%</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="V88">
-        <v>36.46</v>
+        <v>57.62</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -9235,14 +9235,14 @@
         </is>
       </c>
       <c r="X88">
-        <v>-0.0774</v>
+        <v>-0.0534</v>
       </c>
       <c r="Y88">
         <v>0</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>周六016</t>
+          <t>周六018</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>拉齐奥 对 比萨</t>
+          <t>马洛卡 对 奥维耶多</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9313,35 +9313,35 @@
         </is>
       </c>
       <c r="K89">
-        <v>0.6014</v>
+        <v>0.6344</v>
       </c>
       <c r="L89">
-        <v>0.2297</v>
+        <v>0.2207</v>
       </c>
       <c r="M89">
-        <v>0.1689</v>
+        <v>0.1449</v>
       </c>
       <c r="N89">
-        <v>0.6014</v>
+        <v>0.6344</v>
       </c>
       <c r="O89">
-        <v>0.2297</v>
+        <v>0.2207</v>
       </c>
       <c r="P89">
-        <v>0.1689</v>
+        <v>0.1449</v>
       </c>
       <c r="Q89">
-        <v>0.7064</v>
+        <v>0.7056</v>
       </c>
       <c r="R89">
-        <v>0.1832</v>
+        <v>0.1837</v>
       </c>
       <c r="S89">
-        <v>0.1105</v>
+        <v>0.1108</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:11.9% / 2-1:9.8%</t>
+          <t>2-0:13% / 1-0:11.6% / 3-0:9.7%</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9350,7 +9350,7 @@
         </is>
       </c>
       <c r="V89">
-        <v>69.75</v>
+        <v>75.91</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -9358,14 +9358,14 @@
         </is>
       </c>
       <c r="X89">
-        <v>-0.0558</v>
+        <v>-0.07</v>
       </c>
       <c r="Y89">
         <v>0</v>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>周六017</t>
+          <t>周六019</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>赫罗纳 对 埃尔切</t>
+          <t>西班牙人 对 皇家社会</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9436,35 +9436,35 @@
         </is>
       </c>
       <c r="K90">
-        <v>0.5348</v>
+        <v>0.4218</v>
       </c>
       <c r="L90">
-        <v>0.2446</v>
+        <v>0.3097</v>
       </c>
       <c r="M90">
-        <v>0.2206</v>
+        <v>0.2684</v>
       </c>
       <c r="N90">
-        <v>0.5348</v>
+        <v>0.4218</v>
       </c>
       <c r="O90">
-        <v>0.2446</v>
+        <v>0.3097</v>
       </c>
       <c r="P90">
-        <v>0.2206</v>
+        <v>0.2684</v>
       </c>
       <c r="Q90">
-        <v>0.6805</v>
+        <v>0.5114</v>
       </c>
       <c r="R90">
-        <v>0.1961</v>
+        <v>0.2489</v>
       </c>
       <c r="S90">
-        <v>0.1235</v>
+        <v>0.2398</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>2-0:12.7% / 1-0:12.1% / 1-1:9.5%</t>
+          <t>1-1:11.8% / 1-0:11.3% / 2-1:9.4%</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="V90">
-        <v>57.62</v>
+        <v>31.71</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="X90">
-        <v>-0.0534</v>
+        <v>-0.1142</v>
       </c>
       <c r="Y90">
         <v>0</v>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>周六018</t>
+          <t>周六020</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>马洛卡 对 奥维耶多</t>
+          <t>皇马 对 毕尔巴鄂</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -9559,35 +9559,35 @@
         </is>
       </c>
       <c r="K91">
-        <v>0.6344</v>
+        <v>0.6459</v>
       </c>
       <c r="L91">
-        <v>0.2207</v>
+        <v>0.1991</v>
       </c>
       <c r="M91">
-        <v>0.1449</v>
+        <v>0.155</v>
       </c>
       <c r="N91">
-        <v>0.6344</v>
+        <v>0.6459</v>
       </c>
       <c r="O91">
-        <v>0.2207</v>
+        <v>0.1991</v>
       </c>
       <c r="P91">
-        <v>0.1449</v>
+        <v>0.155</v>
       </c>
       <c r="Q91">
-        <v>0.7056</v>
+        <v>0.7118</v>
       </c>
       <c r="R91">
-        <v>0.1837</v>
+        <v>0.1812</v>
       </c>
       <c r="S91">
-        <v>0.1108</v>
+        <v>0.1071</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2-0:13% / 1-0:11.6% / 3-0:9.7%</t>
+          <t>2-0:13.1% / 1-0:12% / 3-0:9.4%</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="V91">
-        <v>75.91</v>
+        <v>79.72</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="X91">
-        <v>-0.07</v>
+        <v>-0.0731</v>
       </c>
       <c r="Y91">
         <v>0</v>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>周六019</t>
+          <t>周六021</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>西班牙人 对 皇家社会</t>
+          <t>赫塔费 对 奥萨苏纳</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9682,44 +9682,44 @@
         </is>
       </c>
       <c r="K92">
-        <v>0.4218</v>
+        <v>0.3645</v>
       </c>
       <c r="L92">
-        <v>0.3097</v>
+        <v>0.3543</v>
       </c>
       <c r="M92">
-        <v>0.2684</v>
+        <v>0.2812</v>
       </c>
       <c r="N92">
-        <v>0.4218</v>
+        <v>0.3645</v>
       </c>
       <c r="O92">
-        <v>0.3097</v>
+        <v>0.3543</v>
       </c>
       <c r="P92">
-        <v>0.2684</v>
+        <v>0.2812</v>
       </c>
       <c r="Q92">
-        <v>0.5114</v>
+        <v>0.444</v>
       </c>
       <c r="R92">
-        <v>0.2489</v>
+        <v>0.2626</v>
       </c>
       <c r="S92">
-        <v>0.2398</v>
+        <v>0.2935</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1-1:11.8% / 1-0:11.3% / 2-1:9.4%</t>
+          <t>1-1:12.5% / 1-0:11.5% / 2-1:8.8%</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V92">
-        <v>31.71</v>
+        <v>16.66</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -9727,14 +9727,14 @@
         </is>
       </c>
       <c r="X92">
-        <v>-0.1142</v>
+        <v>-0.1143</v>
       </c>
       <c r="Y92">
         <v>0</v>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>周六020</t>
+          <t>周六022</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>皇马 对 毕尔巴鄂</t>
+          <t>塞尔塔 对 塞维利亚</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9805,35 +9805,35 @@
         </is>
       </c>
       <c r="K93">
-        <v>0.6459</v>
+        <v>0.5438</v>
       </c>
       <c r="L93">
-        <v>0.1991</v>
+        <v>0.2578</v>
       </c>
       <c r="M93">
-        <v>0.155</v>
+        <v>0.1984</v>
       </c>
       <c r="N93">
-        <v>0.6459</v>
+        <v>0.5438</v>
       </c>
       <c r="O93">
-        <v>0.1991</v>
+        <v>0.2578</v>
       </c>
       <c r="P93">
-        <v>0.155</v>
+        <v>0.1984</v>
       </c>
       <c r="Q93">
-        <v>0.7118</v>
+        <v>0.7044</v>
       </c>
       <c r="R93">
-        <v>0.1812</v>
+        <v>0.1873</v>
       </c>
       <c r="S93">
-        <v>0.1071</v>
+        <v>0.1083</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2-0:13.1% / 1-0:12% / 3-0:9.4%</t>
+          <t>2-0:13.4% / 1-0:12.5% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="V93">
-        <v>79.72</v>
+        <v>57.89</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="X93">
-        <v>-0.0731</v>
+        <v>-0.0538</v>
       </c>
       <c r="Y93">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>周六021</t>
+          <t>周六023</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>赫塔费 对 奥萨苏纳</t>
+          <t>阿拉维斯 对 巴列卡诺</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9928,44 +9928,44 @@
         </is>
       </c>
       <c r="K94">
-        <v>0.3645</v>
+        <v>0.3919</v>
       </c>
       <c r="L94">
-        <v>0.3543</v>
+        <v>0.3108</v>
       </c>
       <c r="M94">
-        <v>0.2812</v>
+        <v>0.2972</v>
       </c>
       <c r="N94">
-        <v>0.3645</v>
+        <v>0.3919</v>
       </c>
       <c r="O94">
-        <v>0.3543</v>
+        <v>0.3108</v>
       </c>
       <c r="P94">
-        <v>0.2812</v>
+        <v>0.2972</v>
       </c>
       <c r="Q94">
-        <v>0.444</v>
+        <v>0.4561</v>
       </c>
       <c r="R94">
-        <v>0.2626</v>
+        <v>0.2581</v>
       </c>
       <c r="S94">
-        <v>0.2935</v>
+        <v>0.2859</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1-1:12.5% / 1-0:11.5% / 2-1:8.8%</t>
+          <t>1-1:12.3% / 1-0:10.7% / 2-1:9.1%</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V94">
-        <v>16.66</v>
+        <v>26.77</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>周六022</t>
+          <t>周六024</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10017,69 +10017,69 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>塞尔塔 对 塞维利亚</t>
+          <t>巴伦西亚 对 巴萨</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
       <c r="I95" t="inlineStr">
         <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>平局-平局</t>
-        </is>
-      </c>
       <c r="K95">
-        <v>0.5438</v>
+        <v>0.2639</v>
       </c>
       <c r="L95">
-        <v>0.2578</v>
+        <v>0.2353</v>
       </c>
       <c r="M95">
-        <v>0.1984</v>
+        <v>0.5008</v>
       </c>
       <c r="N95">
-        <v>0.5438</v>
+        <v>0.2639</v>
       </c>
       <c r="O95">
-        <v>0.2578</v>
+        <v>0.2353</v>
       </c>
       <c r="P95">
-        <v>0.1984</v>
+        <v>0.5008</v>
       </c>
       <c r="Q95">
-        <v>0.7044</v>
+        <v>0.175</v>
       </c>
       <c r="R95">
-        <v>0.1873</v>
+        <v>0.2191</v>
       </c>
       <c r="S95">
-        <v>0.1083</v>
+        <v>0.606</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>2-0:13.4% / 1-0:12.5% / 2-1:9.6%</t>
+          <t>0-1:11.7% / 0-2:10.8% / 1-1:10.3%</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="V95">
-        <v>57.89</v>
+        <v>50.38</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -10096,14 +10096,14 @@
         </is>
       </c>
       <c r="X95">
-        <v>-0.0538</v>
+        <v>-0.073</v>
       </c>
       <c r="Y95">
         <v>0</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>周六023</t>
+          <t>周六025</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>阿拉维斯 对 巴列卡诺</t>
+          <t>贝蒂斯 对 莱万特</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10170,39 +10170,39 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K96">
-        <v>0.3919</v>
+        <v>0.416</v>
       </c>
       <c r="L96">
-        <v>0.3108</v>
+        <v>0.2888</v>
       </c>
       <c r="M96">
-        <v>0.2972</v>
+        <v>0.2951</v>
       </c>
       <c r="N96">
-        <v>0.3919</v>
+        <v>0.416</v>
       </c>
       <c r="O96">
-        <v>0.3108</v>
+        <v>0.2888</v>
       </c>
       <c r="P96">
-        <v>0.2972</v>
+        <v>0.2951</v>
       </c>
       <c r="Q96">
-        <v>0.4561</v>
+        <v>0.4813</v>
       </c>
       <c r="R96">
-        <v>0.2581</v>
+        <v>0.2548</v>
       </c>
       <c r="S96">
-        <v>0.2859</v>
+        <v>0.264</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1-1:12.3% / 1-0:10.7% / 2-1:9.1%</t>
+          <t>1-1:12.1% / 1-0:10.9% / 2-1:9.3%</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="V96">
-        <v>26.77</v>
+        <v>33.83</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -10219,14 +10219,14 @@
         </is>
       </c>
       <c r="X96">
-        <v>-0.1143</v>
+        <v>-0.0557</v>
       </c>
       <c r="Y96">
         <v>0</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10253,79 +10253,79 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>周六024</t>
+          <t>周六026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>巴伦西亚 对 巴萨</t>
+          <t>明尼苏达 对 盐湖城</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>主胜</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
           <t>客胜</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K97">
-        <v>0.2639</v>
+        <v>0.4291</v>
       </c>
       <c r="L97">
-        <v>0.2353</v>
+        <v>0.2591</v>
       </c>
       <c r="M97">
-        <v>0.5008</v>
+        <v>0.3118</v>
       </c>
       <c r="N97">
-        <v>0.2639</v>
+        <v>0.4291</v>
       </c>
       <c r="O97">
-        <v>0.2353</v>
+        <v>0.2591</v>
       </c>
       <c r="P97">
-        <v>0.5008</v>
+        <v>0.3118</v>
       </c>
       <c r="Q97">
-        <v>0.175</v>
+        <v>0.4828</v>
       </c>
       <c r="R97">
-        <v>0.2191</v>
+        <v>0.2442</v>
       </c>
       <c r="S97">
-        <v>0.606</v>
+        <v>0.273</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>0-1:11.7% / 0-2:10.8% / 1-1:10.3%</t>
+          <t>1-1:11.7% / 1-0:10.8% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -10334,7 +10334,7 @@
         </is>
       </c>
       <c r="V97">
-        <v>50.38</v>
+        <v>34.45</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -10342,14 +10342,14 @@
         </is>
       </c>
       <c r="X97">
-        <v>-0.073</v>
+        <v>-0.0813</v>
       </c>
       <c r="Y97">
         <v>0</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>周六025</t>
+          <t>周六027</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>贝蒂斯 对 莱万特</t>
+          <t>夏洛特FC 对 新英格兰</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10416,39 +10416,39 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K98">
-        <v>0.416</v>
+        <v>0.4926</v>
       </c>
       <c r="L98">
-        <v>0.2888</v>
+        <v>0.2556</v>
       </c>
       <c r="M98">
-        <v>0.2951</v>
+        <v>0.2518</v>
       </c>
       <c r="N98">
-        <v>0.416</v>
+        <v>0.4926</v>
       </c>
       <c r="O98">
-        <v>0.2888</v>
+        <v>0.2556</v>
       </c>
       <c r="P98">
-        <v>0.2951</v>
+        <v>0.2518</v>
       </c>
       <c r="Q98">
-        <v>0.4813</v>
+        <v>0.6088</v>
       </c>
       <c r="R98">
-        <v>0.2548</v>
+        <v>0.2245</v>
       </c>
       <c r="S98">
-        <v>0.264</v>
+        <v>0.1667</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1-1:12.1% / 1-0:10.9% / 2-1:9.3%</t>
+          <t>1-0:12.4% / 1-1:10.8% / 2-0:10.6%</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="V98">
-        <v>33.83</v>
+        <v>49.8</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -10465,14 +10465,14 @@
         </is>
       </c>
       <c r="X98">
-        <v>-0.0557</v>
+        <v>-0.0813</v>
       </c>
       <c r="Y98">
         <v>0</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>周六026</t>
+          <t>周六028</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>明尼苏达 对 盐湖城</t>
+          <t>华盛顿 对 蒙特利尔</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10539,39 +10539,39 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K99">
-        <v>0.4291</v>
+        <v>0.4848</v>
       </c>
       <c r="L99">
-        <v>0.2591</v>
+        <v>0.2592</v>
       </c>
       <c r="M99">
-        <v>0.3118</v>
+        <v>0.256</v>
       </c>
       <c r="N99">
-        <v>0.4291</v>
+        <v>0.4848</v>
       </c>
       <c r="O99">
-        <v>0.2591</v>
+        <v>0.2592</v>
       </c>
       <c r="P99">
-        <v>0.3118</v>
+        <v>0.256</v>
       </c>
       <c r="Q99">
-        <v>0.4828</v>
+        <v>0.5995</v>
       </c>
       <c r="R99">
-        <v>0.2442</v>
+        <v>0.2227</v>
       </c>
       <c r="S99">
-        <v>0.273</v>
+        <v>0.1779</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1-1:11.7% / 1-0:10.8% / 2-1:9.6%</t>
+          <t>1-0:11.7% / 2-0:11% / 1-1:10.6%</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="V99">
-        <v>34.45</v>
+        <v>48.21</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -10588,14 +10588,14 @@
         </is>
       </c>
       <c r="X99">
-        <v>-0.0813</v>
+        <v>-0.0803</v>
       </c>
       <c r="Y99">
         <v>0</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>周六027</t>
+          <t>周六029</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>夏洛特FC 对 新英格兰</t>
+          <t>纳什维尔 对 纽约城</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -10666,35 +10666,35 @@
         </is>
       </c>
       <c r="K100">
-        <v>0.4926</v>
+        <v>0.5639</v>
       </c>
       <c r="L100">
-        <v>0.2556</v>
+        <v>0.2393</v>
       </c>
       <c r="M100">
-        <v>0.2518</v>
+        <v>0.1968</v>
       </c>
       <c r="N100">
-        <v>0.4926</v>
+        <v>0.5639</v>
       </c>
       <c r="O100">
-        <v>0.2556</v>
+        <v>0.2393</v>
       </c>
       <c r="P100">
-        <v>0.2518</v>
+        <v>0.1968</v>
       </c>
       <c r="Q100">
-        <v>0.6088</v>
+        <v>0.7065</v>
       </c>
       <c r="R100">
-        <v>0.2245</v>
+        <v>0.1848</v>
       </c>
       <c r="S100">
-        <v>0.1667</v>
+        <v>0.1088</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>1-0:12.4% / 1-1:10.8% / 2-0:10.6%</t>
+          <t>2-0:13.5% / 1-0:12.1% / 2-1:9.2%</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="V100">
-        <v>49.8</v>
+        <v>61.06</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="X100">
-        <v>-0.0813</v>
+        <v>-0.1147</v>
       </c>
       <c r="Y100">
         <v>0</v>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>周六028</t>
+          <t>周六030</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>华盛顿 对 蒙特利尔</t>
+          <t>波特兰 对 圣何塞</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10785,48 +10785,48 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K101">
-        <v>0.4848</v>
+        <v>0.3987</v>
       </c>
       <c r="L101">
-        <v>0.2592</v>
+        <v>0.2408</v>
       </c>
       <c r="M101">
-        <v>0.256</v>
+        <v>0.3605</v>
       </c>
       <c r="N101">
-        <v>0.4848</v>
+        <v>0.3987</v>
       </c>
       <c r="O101">
-        <v>0.2592</v>
+        <v>0.2408</v>
       </c>
       <c r="P101">
-        <v>0.256</v>
+        <v>0.3605</v>
       </c>
       <c r="Q101">
-        <v>0.5995</v>
+        <v>0.4109</v>
       </c>
       <c r="R101">
-        <v>0.2227</v>
+        <v>0.2562</v>
       </c>
       <c r="S101">
-        <v>0.1779</v>
+        <v>0.333</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1-0:11.7% / 2-0:11% / 1-1:10.6%</t>
+          <t>1-1:12.2% / 1-0:10% / 2-1:9%</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V101">
-        <v>48.21</v>
+        <v>23.39</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -10834,14 +10834,14 @@
         </is>
       </c>
       <c r="X101">
-        <v>-0.0803</v>
+        <v>-0.079</v>
       </c>
       <c r="Y101">
         <v>0</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10868,17 +10868,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>周六029</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>纳什维尔 对 纽约城</t>
+          <t>赫尔城 对 南安普敦</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10912,35 +10912,35 @@
         </is>
       </c>
       <c r="K102">
-        <v>0.557</v>
+        <v>0.6828</v>
       </c>
       <c r="L102">
-        <v>0.2426</v>
+        <v>0.1762</v>
       </c>
       <c r="M102">
-        <v>0.2004</v>
+        <v>0.141</v>
       </c>
       <c r="N102">
-        <v>0.557</v>
+        <v>0.6828</v>
       </c>
       <c r="O102">
-        <v>0.2426</v>
+        <v>0.1762</v>
       </c>
       <c r="P102">
-        <v>0.2004</v>
+        <v>0.141</v>
       </c>
       <c r="Q102">
-        <v>0.7061</v>
+        <v>0.7109</v>
       </c>
       <c r="R102">
-        <v>0.185</v>
+        <v>0.1796</v>
       </c>
       <c r="S102">
-        <v>0.109</v>
+        <v>0.1096</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:12.2% / 2-1:9.3%</t>
+          <t>2-0:12.9% / 1-0:11.7% / 3-0:9.4%</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="V102">
-        <v>59.65</v>
+        <v>84.96</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -10957,14 +10957,14 @@
         </is>
       </c>
       <c r="X102">
-        <v>-0.1144</v>
+        <v>-0.0741</v>
       </c>
       <c r="Y102">
         <v>0</v>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：英冠，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>周六030</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>德国杯</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>波特兰 对 圣何塞</t>
+          <t>拜仁慕尼黑 对 斯图加特</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11011,68 +11011,68 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K103">
-        <v>0.3987</v>
+        <v>0.7045</v>
       </c>
       <c r="L103">
-        <v>0.2408</v>
+        <v>0.1655</v>
       </c>
       <c r="M103">
-        <v>0.3605</v>
+        <v>0.13</v>
       </c>
       <c r="N103">
-        <v>0.3987</v>
+        <v>0.2543</v>
       </c>
       <c r="O103">
-        <v>0.2408</v>
+        <v>0.2447</v>
       </c>
       <c r="P103">
-        <v>0.3605</v>
+        <v>0.501</v>
       </c>
       <c r="Q103">
-        <v>0.4109</v>
+        <v>0.1602</v>
       </c>
       <c r="R103">
-        <v>0.2562</v>
+        <v>0.2225</v>
       </c>
       <c r="S103">
-        <v>0.333</v>
+        <v>0.6174</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:10% / 2-1:9%</t>
+          <t>0-1:11.6% / 0-2:11.4% / 1-1:10.8%</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V103">
-        <v>23.39</v>
+        <v>92.23</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
@@ -11080,14 +11080,14 @@
         </is>
       </c>
       <c r="X103">
-        <v>-0.079</v>
+        <v>-0.0566</v>
       </c>
       <c r="Y103">
         <v>0</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11114,79 +11114,79 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>赫尔城 对 南安普敦</t>
+          <t>博洛尼亚 对 国际米兰</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>平局-平局</t>
-        </is>
-      </c>
       <c r="K104">
-        <v>0.6828</v>
+        <v>0.2904</v>
       </c>
       <c r="L104">
-        <v>0.1762</v>
+        <v>0.2531</v>
       </c>
       <c r="M104">
-        <v>0.141</v>
+        <v>0.4565</v>
       </c>
       <c r="N104">
-        <v>0.6828</v>
+        <v>0.627</v>
       </c>
       <c r="O104">
-        <v>0.1762</v>
+        <v>0.2197</v>
       </c>
       <c r="P104">
-        <v>0.141</v>
+        <v>0.1532</v>
       </c>
       <c r="Q104">
-        <v>0.7109</v>
+        <v>0.7036</v>
       </c>
       <c r="R104">
-        <v>0.1796</v>
+        <v>0.188</v>
       </c>
       <c r="S104">
-        <v>0.1096</v>
+        <v>0.1084</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>2-0:12.9% / 1-0:11.7% / 3-0:9.4%</t>
+          <t>2-0:13.3% / 1-0:11.9% / 3-0:9.6%</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="V104">
-        <v>84.96</v>
+        <v>39.07</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -11203,14 +11203,14 @@
         </is>
       </c>
       <c r="X104">
-        <v>-0.0741</v>
+        <v>-0.0651</v>
       </c>
       <c r="Y104">
         <v>0</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>经模型综合分析：英冠，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11237,17 +11237,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>德国杯</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>拜仁慕尼黑 对 斯图加特</t>
+          <t>拉齐奥 对 比萨</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11281,35 +11281,35 @@
         </is>
       </c>
       <c r="K105">
-        <v>0.7045</v>
+        <v>0.6014</v>
       </c>
       <c r="L105">
-        <v>0.1655</v>
+        <v>0.2297</v>
       </c>
       <c r="M105">
-        <v>0.13</v>
+        <v>0.1689</v>
       </c>
       <c r="N105">
-        <v>0.2543</v>
+        <v>0.4947</v>
       </c>
       <c r="O105">
-        <v>0.2447</v>
+        <v>0.2664</v>
       </c>
       <c r="P105">
-        <v>0.501</v>
+        <v>0.239</v>
       </c>
       <c r="Q105">
-        <v>0.1602</v>
+        <v>0.6228</v>
       </c>
       <c r="R105">
-        <v>0.2225</v>
+        <v>0.2126</v>
       </c>
       <c r="S105">
-        <v>0.6174</v>
+        <v>0.1647</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>0-1:11.6% / 0-2:11.4% / 1-1:10.8%</t>
+          <t>1-0:11.9% / 2-0:11.6% / 1-1:9.9%</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="V105">
-        <v>92.23</v>
+        <v>69.75</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -11326,14 +11326,14 @@
         </is>
       </c>
       <c r="X105">
-        <v>-0.0566</v>
+        <v>-0.065</v>
       </c>
       <c r="Y105">
         <v>0</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11360,79 +11360,79 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>博洛尼亚 对 国际米兰</t>
+          <t>维戈塞尔塔 对 塞维利亚</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K106">
-        <v>0.2785</v>
+        <v>0.5438</v>
       </c>
       <c r="L106">
-        <v>0.253</v>
+        <v>0.2578</v>
       </c>
       <c r="M106">
-        <v>0.4685</v>
+        <v>0.1984</v>
       </c>
       <c r="N106">
-        <v>0.627</v>
+        <v>0.3949</v>
       </c>
       <c r="O106">
-        <v>0.2197</v>
+        <v>0.3331</v>
       </c>
       <c r="P106">
-        <v>0.1532</v>
+        <v>0.272</v>
       </c>
       <c r="Q106">
-        <v>0.7036</v>
+        <v>0.482</v>
       </c>
       <c r="R106">
-        <v>0.188</v>
+        <v>0.2551</v>
       </c>
       <c r="S106">
-        <v>0.1084</v>
+        <v>0.2629</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>2-0:13.3% / 1-0:11.9% / 3-0:9.6%</t>
+          <t>1-1:12.2% / 1-0:11.4% / 2-1:9.4%</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="V106">
-        <v>42.08</v>
+        <v>57.89</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -11449,14 +11449,14 @@
         </is>
       </c>
       <c r="X106">
-        <v>-0.0651</v>
+        <v>-0.0645</v>
       </c>
       <c r="Y106">
         <v>0</v>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11483,17 +11483,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>拉齐奥 对 比萨</t>
+          <t>赫塔费 对 奥萨苏纳</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -11527,44 +11527,44 @@
         </is>
       </c>
       <c r="K107">
-        <v>0.6014</v>
+        <v>0.3645</v>
       </c>
       <c r="L107">
-        <v>0.2297</v>
+        <v>0.3543</v>
       </c>
       <c r="M107">
-        <v>0.1689</v>
+        <v>0.2812</v>
       </c>
       <c r="N107">
-        <v>0.4947</v>
+        <v>0.5101</v>
       </c>
       <c r="O107">
-        <v>0.2664</v>
+        <v>0.2496</v>
       </c>
       <c r="P107">
-        <v>0.239</v>
+        <v>0.2402</v>
       </c>
       <c r="Q107">
-        <v>0.6228</v>
+        <v>0.6407</v>
       </c>
       <c r="R107">
-        <v>0.2126</v>
+        <v>0.2083</v>
       </c>
       <c r="S107">
-        <v>0.1647</v>
+        <v>0.1511</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1-0:11.9% / 2-0:11.6% / 1-1:9.9%</t>
+          <t>1-0:12.4% / 2-0:12% / 1-1:10.1%</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V107">
-        <v>69.75</v>
+        <v>16.66</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>
@@ -11572,14 +11572,14 @@
         </is>
       </c>
       <c r="X107">
-        <v>-0.065</v>
+        <v>-0.066</v>
       </c>
       <c r="Y107">
         <v>0</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>维戈塞尔塔 对 塞维利亚</t>
+          <t>赫罗纳 对 埃尔切</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11650,35 +11650,35 @@
         </is>
       </c>
       <c r="K108">
-        <v>0.5438</v>
+        <v>0.5348</v>
       </c>
       <c r="L108">
-        <v>0.2578</v>
+        <v>0.2446</v>
       </c>
       <c r="M108">
-        <v>0.1984</v>
+        <v>0.2206</v>
       </c>
       <c r="N108">
-        <v>0.3949</v>
+        <v>0.4605</v>
       </c>
       <c r="O108">
-        <v>0.3331</v>
+        <v>0.2536</v>
       </c>
       <c r="P108">
-        <v>0.272</v>
+        <v>0.2859</v>
       </c>
       <c r="Q108">
-        <v>0.482</v>
+        <v>0.5475</v>
       </c>
       <c r="R108">
-        <v>0.2551</v>
+        <v>0.2369</v>
       </c>
       <c r="S108">
-        <v>0.2629</v>
+        <v>0.2157</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:11.4% / 2-1:9.4%</t>
+          <t>1-0:11.4% / 1-1:11% / 2-1:9.9%</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -11687,7 +11687,7 @@
         </is>
       </c>
       <c r="V108">
-        <v>57.89</v>
+        <v>57.62</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -11695,14 +11695,14 @@
         </is>
       </c>
       <c r="X108">
-        <v>-0.0645</v>
+        <v>-0.0606</v>
       </c>
       <c r="Y108">
         <v>0</v>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11729,17 +11729,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>荷乙</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>赫塔费 对 奥萨苏纳</t>
+          <t>福伦丹 对 威廉二世</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -11769,48 +11769,48 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K109">
-        <v>0.3645</v>
+        <v>0.4352</v>
       </c>
       <c r="L109">
-        <v>0.3543</v>
+        <v>0.2643</v>
       </c>
       <c r="M109">
-        <v>0.2812</v>
+        <v>0.3005</v>
       </c>
       <c r="N109">
-        <v>0.5101</v>
+        <v>0.3999</v>
       </c>
       <c r="O109">
-        <v>0.2496</v>
+        <v>0.2717</v>
       </c>
       <c r="P109">
-        <v>0.2402</v>
+        <v>0.3284</v>
       </c>
       <c r="Q109">
-        <v>0.6407</v>
+        <v>0.44</v>
       </c>
       <c r="R109">
-        <v>0.2083</v>
+        <v>0.2542</v>
       </c>
       <c r="S109">
-        <v>0.1511</v>
+        <v>0.3059</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1-0:12.4% / 2-0:12% / 1-1:10.1%</t>
+          <t>1-1:11.9% / 1-0:10.1% / 2-1:9.2%</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V109">
-        <v>16.66</v>
+        <v>36.46</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11818,14 +11818,14 @@
         </is>
       </c>
       <c r="X109">
-        <v>-0.066</v>
+        <v>-0.079</v>
       </c>
       <c r="Y109">
         <v>0</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11852,17 +11852,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>赫罗纳 对 埃尔切</t>
+          <t>哈尔姆斯塔德 对 厄尔格里特</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -11892,39 +11892,39 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K110">
-        <v>0.5348</v>
+        <v>0.4354</v>
       </c>
       <c r="L110">
-        <v>0.2446</v>
+        <v>0.2737</v>
       </c>
       <c r="M110">
-        <v>0.2206</v>
+        <v>0.291</v>
       </c>
       <c r="N110">
-        <v>0.4605</v>
+        <v>0.4354</v>
       </c>
       <c r="O110">
-        <v>0.2536</v>
+        <v>0.2737</v>
       </c>
       <c r="P110">
-        <v>0.2859</v>
+        <v>0.291</v>
       </c>
       <c r="Q110">
-        <v>0.5475</v>
+        <v>0.511</v>
       </c>
       <c r="R110">
-        <v>0.2369</v>
+        <v>0.2464</v>
       </c>
       <c r="S110">
-        <v>0.2157</v>
+        <v>0.2427</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1-0:11.4% / 1-1:11% / 2-1:9.9%</t>
+          <t>1-1:12% / 1-0:11.3% / 2-1:9.2%</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -11933,7 +11933,7 @@
         </is>
       </c>
       <c r="V110">
-        <v>57.62</v>
+        <v>34.54</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -11941,14 +11941,14 @@
         </is>
       </c>
       <c r="X110">
-        <v>-0.0606</v>
+        <v>-0.0804</v>
       </c>
       <c r="Y110">
         <v>0</v>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11975,17 +11975,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>福伦丹 对 威廉二世</t>
+          <t>卡尔马 对 代格福什</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -12015,39 +12015,39 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K111">
-        <v>0.4352</v>
+        <v>0.4445</v>
       </c>
       <c r="L111">
-        <v>0.2643</v>
+        <v>0.291</v>
       </c>
       <c r="M111">
-        <v>0.3005</v>
+        <v>0.2645</v>
       </c>
       <c r="N111">
-        <v>0.3999</v>
+        <v>0.4445</v>
       </c>
       <c r="O111">
-        <v>0.2717</v>
+        <v>0.291</v>
       </c>
       <c r="P111">
-        <v>0.3284</v>
+        <v>0.2645</v>
       </c>
       <c r="Q111">
-        <v>0.44</v>
+        <v>0.5478</v>
       </c>
       <c r="R111">
-        <v>0.2542</v>
+        <v>0.2373</v>
       </c>
       <c r="S111">
-        <v>0.3059</v>
+        <v>0.2149</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1-1:11.9% / 1-0:10.1% / 2-1:9.2%</t>
+          <t>1-1:11.3% / 1-0:11.3% / 2-0:10.3%</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -12056,7 +12056,7 @@
         </is>
       </c>
       <c r="V111">
-        <v>36.46</v>
+        <v>36.02</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -12064,14 +12064,14 @@
         </is>
       </c>
       <c r="X111">
-        <v>-0.079</v>
+        <v>-0.0812</v>
       </c>
       <c r="Y111">
         <v>0</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12098,17 +12098,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>哈尔姆斯塔德 对 厄尔格里特</t>
+          <t>坦佩雷山猫 对 赫尔辛基火花</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -12142,35 +12142,35 @@
         </is>
       </c>
       <c r="K112">
-        <v>0.4354</v>
+        <v>0.5009</v>
       </c>
       <c r="L112">
-        <v>0.2737</v>
+        <v>0.2465</v>
       </c>
       <c r="M112">
-        <v>0.291</v>
+        <v>0.2526</v>
       </c>
       <c r="N112">
-        <v>0.4354</v>
+        <v>0.521</v>
       </c>
       <c r="O112">
-        <v>0.2737</v>
+        <v>0.2408</v>
       </c>
       <c r="P112">
-        <v>0.291</v>
+        <v>0.2382</v>
       </c>
       <c r="Q112">
-        <v>0.511</v>
+        <v>0.6562</v>
       </c>
       <c r="R112">
-        <v>0.2464</v>
+        <v>0.2042</v>
       </c>
       <c r="S112">
-        <v>0.2427</v>
+        <v>0.1396</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>1-1:12% / 1-0:11.3% / 2-1:9.2%</t>
+          <t>1-0:12.4% / 2-0:11.8% / 1-1:10.2%</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -12179,7 +12179,7 @@
         </is>
       </c>
       <c r="V112">
-        <v>34.54</v>
+        <v>51.41</v>
       </c>
       <c r="W112" t="inlineStr">
         <is>
@@ -12187,14 +12187,14 @@
         </is>
       </c>
       <c r="X112">
-        <v>-0.0804</v>
+        <v>-0.0737</v>
       </c>
       <c r="Y112">
         <v>0</v>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12221,17 +12221,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>卡尔马 对 代格福什</t>
+          <t>雅罗 对 玛丽港</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -12265,35 +12265,35 @@
         </is>
       </c>
       <c r="K113">
-        <v>0.4872</v>
+        <v>0.4828</v>
       </c>
       <c r="L113">
-        <v>0.2814</v>
+        <v>0.272</v>
       </c>
       <c r="M113">
-        <v>0.2314</v>
+        <v>0.2452</v>
       </c>
       <c r="N113">
-        <v>0.4445</v>
+        <v>0.4923</v>
       </c>
       <c r="O113">
-        <v>0.291</v>
+        <v>0.2635</v>
       </c>
       <c r="P113">
-        <v>0.2645</v>
+        <v>0.2441</v>
       </c>
       <c r="Q113">
-        <v>0.5478</v>
+        <v>0.615</v>
       </c>
       <c r="R113">
-        <v>0.2373</v>
+        <v>0.2164</v>
       </c>
       <c r="S113">
-        <v>0.2149</v>
+        <v>0.1687</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1-1:11.3% / 1-0:11.3% / 2-0:10.3%</t>
+          <t>1-0:12.1% / 2-0:11.7% / 1-1:10%</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -12302,7 +12302,7 @@
         </is>
       </c>
       <c r="V113">
-        <v>46.6</v>
+        <v>46.73</v>
       </c>
       <c r="W113" t="inlineStr">
         <is>
@@ -12310,14 +12310,14 @@
         </is>
       </c>
       <c r="X113">
-        <v>-0.0812</v>
+        <v>-0.0814</v>
       </c>
       <c r="Y113">
         <v>0</v>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六007 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12344,7 +12344,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>坦佩雷山猫 对 赫尔辛基火花</t>
+          <t>库奥皮奥 对 拉赫蒂</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12364,17 +12364,17 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -12384,39 +12384,39 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K114">
-        <v>0.5009</v>
+        <v>0.5934</v>
       </c>
       <c r="L114">
-        <v>0.2465</v>
+        <v>0.2361</v>
       </c>
       <c r="M114">
-        <v>0.2526</v>
+        <v>0.1705</v>
       </c>
       <c r="N114">
-        <v>0.521</v>
+        <v>0.5759</v>
       </c>
       <c r="O114">
-        <v>0.2408</v>
+        <v>0.2432</v>
       </c>
       <c r="P114">
-        <v>0.2382</v>
+        <v>0.181</v>
       </c>
       <c r="Q114">
-        <v>0.6562</v>
+        <v>0.7019</v>
       </c>
       <c r="R114">
-        <v>0.2042</v>
+        <v>0.1851</v>
       </c>
       <c r="S114">
-        <v>0.1396</v>
+        <v>0.113</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1-0:12.4% / 2-0:11.8% / 1-1:10.2%</t>
+          <t>2-0:12.6% / 1-0:12.5% / 3-0:9.6%</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -12425,7 +12425,7 @@
         </is>
       </c>
       <c r="V114">
-        <v>51.41</v>
+        <v>67.88</v>
       </c>
       <c r="W114" t="inlineStr">
         <is>
@@ -12433,14 +12433,14 @@
         </is>
       </c>
       <c r="X114">
-        <v>-0.0737</v>
+        <v>-0.0837</v>
       </c>
       <c r="Y114">
         <v>0</v>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>雅罗 对 玛丽港</t>
+          <t>塞伊奈约基 对 AC 奥卢</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -12507,48 +12507,48 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K115">
-        <v>0.4828</v>
+        <v>0.3731</v>
       </c>
       <c r="L115">
-        <v>0.272</v>
+        <v>0.2676</v>
       </c>
       <c r="M115">
-        <v>0.2452</v>
+        <v>0.3593</v>
       </c>
       <c r="N115">
-        <v>0.4923</v>
+        <v>0.369</v>
       </c>
       <c r="O115">
-        <v>0.2635</v>
+        <v>0.2689</v>
       </c>
       <c r="P115">
-        <v>0.2441</v>
+        <v>0.362</v>
       </c>
       <c r="Q115">
-        <v>0.615</v>
+        <v>0.3796</v>
       </c>
       <c r="R115">
-        <v>0.2164</v>
+        <v>0.2597</v>
       </c>
       <c r="S115">
-        <v>0.1687</v>
+        <v>0.3607</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1-0:12.1% / 2-0:11.7% / 1-1:10%</t>
+          <t>1-1:12.4% / 1-0:9.5% / 0-1:9.2%</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V115">
-        <v>46.73</v>
+        <v>19.36</v>
       </c>
       <c r="W115" t="inlineStr">
         <is>
@@ -12556,14 +12556,14 @@
         </is>
       </c>
       <c r="X115">
-        <v>-0.0814</v>
+        <v>-0.0834</v>
       </c>
       <c r="Y115">
         <v>0</v>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12577,258 +12577,12 @@
         </is>
       </c>
       <c r="AC115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>库奥皮奥 对 拉赫蒂</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>平局-平局</t>
-        </is>
-      </c>
-      <c r="K116">
-        <v>0.5934</v>
-      </c>
-      <c r="L116">
-        <v>0.2361</v>
-      </c>
-      <c r="M116">
-        <v>0.1705</v>
-      </c>
-      <c r="N116">
-        <v>0.5759</v>
-      </c>
-      <c r="O116">
-        <v>0.2432</v>
-      </c>
-      <c r="P116">
-        <v>0.181</v>
-      </c>
-      <c r="Q116">
-        <v>0.7019</v>
-      </c>
-      <c r="R116">
-        <v>0.1851</v>
-      </c>
-      <c r="S116">
-        <v>0.113</v>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>2-0:12.6% / 1-0:12.5% / 3-0:9.6%</t>
-        </is>
-      </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="V116">
-        <v>67.88</v>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X116">
-        <v>-0.0837</v>
-      </c>
-      <c r="Y116">
-        <v>0</v>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>塞伊奈约基 对 AC 奥卢</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>平局-客胜</t>
-        </is>
-      </c>
-      <c r="K117">
-        <v>0.3731</v>
-      </c>
-      <c r="L117">
-        <v>0.2676</v>
-      </c>
-      <c r="M117">
-        <v>0.3593</v>
-      </c>
-      <c r="N117">
-        <v>0.369</v>
-      </c>
-      <c r="O117">
-        <v>0.2689</v>
-      </c>
-      <c r="P117">
-        <v>0.362</v>
-      </c>
-      <c r="Q117">
-        <v>0.3796</v>
-      </c>
-      <c r="R117">
-        <v>0.2597</v>
-      </c>
-      <c r="S117">
-        <v>0.3607</v>
-      </c>
-      <c r="T117" t="inlineStr">
-        <is>
-          <t>1-1:12.4% / 1-0:9.5% / 0-1:9.2%</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="V117">
-        <v>19.36</v>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X117">
-        <v>-0.0834</v>
-      </c>
-      <c r="Y117">
-        <v>0</v>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD117"/>
+  <autoFilter ref="A1:AD115"/>
 </worksheet>
 </file>
--- a/data/exports/football-recap-master.xlsx
+++ b/data/exports/football-recap-master.xlsx
@@ -8556,12 +8556,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="V83">
-        <v>43.94</v>
+        <v>48.14</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K84">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="V84">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="V90">
-        <v>31.71</v>
+        <v>35.91</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9663,12 +9663,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="V92">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -9919,12 +9919,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K94">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="V94">
-        <v>26.77</v>
+        <v>30.97</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -10647,22 +10647,22 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K100">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="V100">
-        <v>61.06</v>
+        <v>65.26</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="V104">
-        <v>39.07</v>
+        <v>43.27</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="V107">
-        <v>16.66</v>
+        <v>20.86</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>

--- a/data/exports/football-recap-master.xlsx
+++ b/data/exports/football-recap-master.xlsx
@@ -8556,12 +8556,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8575,35 +8575,35 @@
         </is>
       </c>
       <c r="K83">
-        <v>0.2231</v>
+        <v>0.216</v>
       </c>
       <c r="L83">
-        <v>0.2904</v>
+        <v>0.2838</v>
       </c>
       <c r="M83">
-        <v>0.4866</v>
+        <v>0.5002</v>
       </c>
       <c r="N83">
-        <v>0.2231</v>
+        <v>0.216</v>
       </c>
       <c r="O83">
-        <v>0.2904</v>
+        <v>0.2838</v>
       </c>
       <c r="P83">
-        <v>0.4866</v>
+        <v>0.5002</v>
       </c>
       <c r="Q83">
-        <v>0.1558</v>
+        <v>0.142</v>
       </c>
       <c r="R83">
-        <v>0.214</v>
+        <v>0.2056</v>
       </c>
       <c r="S83">
-        <v>0.6303</v>
+        <v>0.6525</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>0-1:12.3% / 0-2:11.9% / 1-2:10.1%</t>
+          <t>0-1:12.4% / 0-2:12.3% / 1-2:9.7%</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="V83">
-        <v>48.14</v>
+        <v>46.74</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="X83">
-        <v>-0.1144</v>
+        <v>-0.1146</v>
       </c>
       <c r="Y83">
         <v>0</v>
@@ -8684,7 +8684,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8694,39 +8694,39 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="K84">
-        <v>0.2904</v>
+        <v>0.3001</v>
       </c>
       <c r="L84">
-        <v>0.2531</v>
+        <v>0.2529</v>
       </c>
       <c r="M84">
-        <v>0.4565</v>
+        <v>0.447</v>
       </c>
       <c r="N84">
-        <v>0.2904</v>
+        <v>0.3001</v>
       </c>
       <c r="O84">
-        <v>0.2531</v>
+        <v>0.2529</v>
       </c>
       <c r="P84">
-        <v>0.4565</v>
+        <v>0.447</v>
       </c>
       <c r="Q84">
-        <v>0.2243</v>
+        <v>0.2415</v>
       </c>
       <c r="R84">
-        <v>0.2405</v>
+        <v>0.241</v>
       </c>
       <c r="S84">
-        <v>0.5353</v>
+        <v>0.5176</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1-1:11.5% / 0-1:10.9% / 1-2:10%</t>
+          <t>1-1:11.2% / 0-1:10.8% / 1-2:10%</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="V84">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="X84">
-        <v>-0.1144</v>
+        <v>-0.1149</v>
       </c>
       <c r="Y84">
         <v>0</v>
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="V90">
-        <v>35.91</v>
+        <v>31.71</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9663,12 +9663,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="V92">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -9919,12 +9919,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K94">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="V94">
-        <v>30.97</v>
+        <v>26.77</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -10647,22 +10647,22 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K100">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="V100">
-        <v>65.26</v>
+        <v>61.06</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -11158,13 +11158,13 @@
         </is>
       </c>
       <c r="K104">
-        <v>0.2904</v>
+        <v>0.3001</v>
       </c>
       <c r="L104">
-        <v>0.2531</v>
+        <v>0.2529</v>
       </c>
       <c r="M104">
-        <v>0.4565</v>
+        <v>0.447</v>
       </c>
       <c r="N104">
         <v>0.627</v>
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="V104">
-        <v>43.27</v>
+        <v>36.66</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="V107">
-        <v>20.86</v>
+        <v>16.66</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>

--- a/data/exports/football-recap-master.xlsx
+++ b/data/exports/football-recap-master.xlsx
@@ -8039,79 +8039,79 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>周六008</t>
+          <t>周六012</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>坦山猫 对 赫尔火花</t>
+          <t>赫尔城 对 米堡</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K79">
-        <v>0.5009</v>
+        <v>0.216</v>
       </c>
       <c r="L79">
-        <v>0.2465</v>
+        <v>0.2838</v>
       </c>
       <c r="M79">
-        <v>0.2526</v>
+        <v>0.5002</v>
       </c>
       <c r="N79">
-        <v>0.5009</v>
+        <v>0.216</v>
       </c>
       <c r="O79">
-        <v>0.2465</v>
+        <v>0.2838</v>
       </c>
       <c r="P79">
-        <v>0.2526</v>
+        <v>0.5002</v>
       </c>
       <c r="Q79">
-        <v>0.6198</v>
+        <v>0.1932</v>
       </c>
       <c r="R79">
-        <v>0.2187</v>
+        <v>0.2242</v>
       </c>
       <c r="S79">
-        <v>0.1616</v>
+        <v>0.5826</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1-0:12.1% / 2-0:11.5% / 1-1:10.5%</t>
+          <t>0-1:11.6% / 1-1:10.5% / 0-2:10.5%</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="V79">
-        <v>51.41</v>
+        <v>50.94</v>
       </c>
       <c r="W79" t="inlineStr">
         <is>
@@ -8128,14 +8128,14 @@
         </is>
       </c>
       <c r="X79">
-        <v>-0.0638</v>
+        <v>-0.1146</v>
       </c>
       <c r="Y79">
         <v>0</v>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：英冠，客胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8162,88 +8162,88 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>周六009</t>
+          <t>周六013</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>塞伊奈 对 AC奥卢</t>
+          <t>博洛尼亚 对 国际米兰</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="I80" t="inlineStr">
         <is>
+          <t>客胜-客胜</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>客胜-客胜</t>
-        </is>
-      </c>
       <c r="K80">
-        <v>0.3731</v>
+        <v>0.3001</v>
       </c>
       <c r="L80">
-        <v>0.2676</v>
+        <v>0.2529</v>
       </c>
       <c r="M80">
-        <v>0.3593</v>
+        <v>0.447</v>
       </c>
       <c r="N80">
-        <v>0.3731</v>
+        <v>0.3001</v>
       </c>
       <c r="O80">
-        <v>0.2676</v>
+        <v>0.2529</v>
       </c>
       <c r="P80">
-        <v>0.3593</v>
+        <v>0.447</v>
       </c>
       <c r="Q80">
-        <v>0.3832</v>
+        <v>0.2768</v>
       </c>
       <c r="R80">
-        <v>0.2598</v>
+        <v>0.246</v>
       </c>
       <c r="S80">
-        <v>0.3571</v>
+        <v>0.4773</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1-1:12.6% / 1-0:10% / 0-1:9%</t>
+          <t>1-1:11.3% / 0-1:10.4% / 1-2:9.8%</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V80">
-        <v>19.36</v>
+        <v>40.86</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
@@ -8251,14 +8251,14 @@
         </is>
       </c>
       <c r="X80">
-        <v>-0.0777</v>
+        <v>-0.1149</v>
       </c>
       <c r="Y80">
         <v>0</v>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>周六010</t>
+          <t>周六014</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>德国杯</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>库奥皮奥 对 拉赫蒂</t>
+          <t>拜仁 对 斯图加特</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8329,35 +8329,35 @@
         </is>
       </c>
       <c r="K81">
-        <v>0.5934</v>
+        <v>0.7045</v>
       </c>
       <c r="L81">
-        <v>0.2361</v>
+        <v>0.1655</v>
       </c>
       <c r="M81">
-        <v>0.1705</v>
+        <v>0.13</v>
       </c>
       <c r="N81">
-        <v>0.5934</v>
+        <v>0.7045</v>
       </c>
       <c r="O81">
-        <v>0.2361</v>
+        <v>0.1655</v>
       </c>
       <c r="P81">
-        <v>0.1705</v>
+        <v>0.13</v>
       </c>
       <c r="Q81">
-        <v>0.7053</v>
+        <v>0.6747</v>
       </c>
       <c r="R81">
-        <v>0.1834</v>
+        <v>0.1917</v>
       </c>
       <c r="S81">
-        <v>0.1114</v>
+        <v>0.1337</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>2-0:13.1% / 1-0:11.9% / 3-0:9.6%</t>
+          <t>2-0:11.9% / 1-0:10.6% / 2-1:9.8%</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="V81">
-        <v>67.88</v>
+        <v>96.43</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
@@ -8374,14 +8374,14 @@
         </is>
       </c>
       <c r="X81">
-        <v>-0.0743</v>
+        <v>-0.063</v>
       </c>
       <c r="Y81">
         <v>0</v>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8408,17 +8408,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>周六011</t>
+          <t>周六015</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>芬超</t>
+          <t>荷乙</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>雅罗 对 玛丽港</t>
+          <t>福伦丹 对 威廉二世</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8448,39 +8448,39 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K82">
-        <v>0.4828</v>
+        <v>0.4352</v>
       </c>
       <c r="L82">
-        <v>0.272</v>
+        <v>0.2643</v>
       </c>
       <c r="M82">
-        <v>0.2452</v>
+        <v>0.3005</v>
       </c>
       <c r="N82">
-        <v>0.4828</v>
+        <v>0.4352</v>
       </c>
       <c r="O82">
-        <v>0.272</v>
+        <v>0.2643</v>
       </c>
       <c r="P82">
-        <v>0.2452</v>
+        <v>0.3005</v>
       </c>
       <c r="Q82">
-        <v>0.6085</v>
+        <v>0.4707</v>
       </c>
       <c r="R82">
-        <v>0.2202</v>
+        <v>0.2498</v>
       </c>
       <c r="S82">
-        <v>0.1714</v>
+        <v>0.2796</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1-0:11.7% / 2-0:11.1% / 1-1:10.5%</t>
+          <t>1-1:11.8% / 1-0:10.4% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="V82">
-        <v>46.73</v>
+        <v>40.66</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
@@ -8497,14 +8497,14 @@
         </is>
       </c>
       <c r="X82">
-        <v>-0.0779</v>
+        <v>-0.0774</v>
       </c>
       <c r="Y82">
         <v>0</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -8531,22 +8531,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>周六012</t>
+          <t>周六016</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>赫尔城 对 米堡</t>
+          <t>拉齐奥 对 比萨</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8556,17 +8556,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8575,35 +8575,35 @@
         </is>
       </c>
       <c r="K83">
-        <v>0.216</v>
+        <v>0.6014</v>
       </c>
       <c r="L83">
-        <v>0.2838</v>
+        <v>0.2297</v>
       </c>
       <c r="M83">
-        <v>0.5002</v>
+        <v>0.1689</v>
       </c>
       <c r="N83">
-        <v>0.216</v>
+        <v>0.6014</v>
       </c>
       <c r="O83">
-        <v>0.2838</v>
+        <v>0.2297</v>
       </c>
       <c r="P83">
-        <v>0.5002</v>
+        <v>0.1689</v>
       </c>
       <c r="Q83">
-        <v>0.142</v>
+        <v>0.6629</v>
       </c>
       <c r="R83">
-        <v>0.2056</v>
+        <v>0.202</v>
       </c>
       <c r="S83">
-        <v>0.6525</v>
+        <v>0.1352</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>0-1:12.4% / 0-2:12.3% / 1-2:9.7%</t>
+          <t>2-0:12.3% / 1-0:11.4% / 2-1:10.1%</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="V83">
-        <v>46.74</v>
+        <v>73.95</v>
       </c>
       <c r="W83" t="inlineStr">
         <is>
@@ -8620,14 +8620,14 @@
         </is>
       </c>
       <c r="X83">
-        <v>-0.1146</v>
+        <v>-0.0558</v>
       </c>
       <c r="Y83">
         <v>0</v>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>经模型综合分析：英冠，客胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -8654,79 +8654,79 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>周六013</t>
+          <t>周六017</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>博洛尼亚 对 国际米兰</t>
+          <t>赫罗纳 对 埃尔切</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K84">
-        <v>0.3001</v>
+        <v>0.5348</v>
       </c>
       <c r="L84">
-        <v>0.2529</v>
+        <v>0.2446</v>
       </c>
       <c r="M84">
-        <v>0.447</v>
+        <v>0.2206</v>
       </c>
       <c r="N84">
-        <v>0.3001</v>
+        <v>0.5348</v>
       </c>
       <c r="O84">
-        <v>0.2529</v>
+        <v>0.2446</v>
       </c>
       <c r="P84">
-        <v>0.447</v>
+        <v>0.2206</v>
       </c>
       <c r="Q84">
-        <v>0.2415</v>
+        <v>0.6015</v>
       </c>
       <c r="R84">
-        <v>0.241</v>
+        <v>0.2198</v>
       </c>
       <c r="S84">
-        <v>0.5176</v>
+        <v>0.1788</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1-1:11.2% / 0-1:10.8% / 1-2:10%</t>
+          <t>1-0:11.2% / 2-0:10.5% / 1-1:10.2%</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="V84">
-        <v>36.66</v>
+        <v>61.82</v>
       </c>
       <c r="W84" t="inlineStr">
         <is>
@@ -8743,14 +8743,14 @@
         </is>
       </c>
       <c r="X84">
-        <v>-0.1149</v>
+        <v>-0.0534</v>
       </c>
       <c r="Y84">
         <v>0</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -8777,17 +8777,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>周六014</t>
+          <t>周六018</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>德国杯</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>拜仁 对 斯图加特</t>
+          <t>马洛卡 对 奥维耶多</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8821,35 +8821,35 @@
         </is>
       </c>
       <c r="K85">
-        <v>0.7045</v>
+        <v>0.6344</v>
       </c>
       <c r="L85">
-        <v>0.1655</v>
+        <v>0.2207</v>
       </c>
       <c r="M85">
-        <v>0.13</v>
+        <v>0.1449</v>
       </c>
       <c r="N85">
-        <v>0.7045</v>
+        <v>0.6344</v>
       </c>
       <c r="O85">
-        <v>0.1655</v>
+        <v>0.2207</v>
       </c>
       <c r="P85">
-        <v>0.13</v>
+        <v>0.1449</v>
       </c>
       <c r="Q85">
-        <v>0.711</v>
+        <v>0.6635</v>
       </c>
       <c r="R85">
-        <v>0.1764</v>
+        <v>0.2001</v>
       </c>
       <c r="S85">
-        <v>0.1127</v>
+        <v>0.1364</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>2-0:12.6% / 1-0:11.1% / 2-1:9.7%</t>
+          <t>2-0:12.1% / 1-0:11% / 2-1:9.5%</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="V85">
-        <v>92.23</v>
+        <v>80.11</v>
       </c>
       <c r="W85" t="inlineStr">
         <is>
@@ -8866,14 +8866,14 @@
         </is>
       </c>
       <c r="X85">
-        <v>-0.063</v>
+        <v>-0.07</v>
       </c>
       <c r="Y85">
         <v>0</v>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -8900,17 +8900,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>周六015</t>
+          <t>周六019</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>福伦丹 对 威廉二世</t>
+          <t>西班牙人 对 皇家社会</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -8940,39 +8940,39 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K86">
-        <v>0.4352</v>
+        <v>0.4218</v>
       </c>
       <c r="L86">
-        <v>0.2643</v>
+        <v>0.3097</v>
       </c>
       <c r="M86">
-        <v>0.3005</v>
+        <v>0.2684</v>
       </c>
       <c r="N86">
-        <v>0.4352</v>
+        <v>0.4218</v>
       </c>
       <c r="O86">
-        <v>0.2643</v>
+        <v>0.3097</v>
       </c>
       <c r="P86">
-        <v>0.3005</v>
+        <v>0.2684</v>
       </c>
       <c r="Q86">
-        <v>0.504</v>
+        <v>0.4742</v>
       </c>
       <c r="R86">
-        <v>0.2456</v>
+        <v>0.2537</v>
       </c>
       <c r="S86">
-        <v>0.2504</v>
+        <v>0.2721</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1-1:11.7% / 1-0:10.9% / 2-1:9.8%</t>
+          <t>1-1:12.4% / 1-0:10.7% / 2-1:9.2%</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -8981,7 +8981,7 @@
         </is>
       </c>
       <c r="V86">
-        <v>36.46</v>
+        <v>35.91</v>
       </c>
       <c r="W86" t="inlineStr">
         <is>
@@ -8989,14 +8989,14 @@
         </is>
       </c>
       <c r="X86">
-        <v>-0.0774</v>
+        <v>-0.1142</v>
       </c>
       <c r="Y86">
         <v>0</v>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9023,17 +9023,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>周六016</t>
+          <t>周六020</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>拉齐奥 对 比萨</t>
+          <t>皇马 对 毕尔巴鄂</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -9067,35 +9067,35 @@
         </is>
       </c>
       <c r="K87">
-        <v>0.6014</v>
+        <v>0.6459</v>
       </c>
       <c r="L87">
-        <v>0.2297</v>
+        <v>0.1991</v>
       </c>
       <c r="M87">
-        <v>0.1689</v>
+        <v>0.155</v>
       </c>
       <c r="N87">
-        <v>0.6014</v>
+        <v>0.6459</v>
       </c>
       <c r="O87">
-        <v>0.2297</v>
+        <v>0.1991</v>
       </c>
       <c r="P87">
-        <v>0.1689</v>
+        <v>0.155</v>
       </c>
       <c r="Q87">
-        <v>0.7064</v>
+        <v>0.6687</v>
       </c>
       <c r="R87">
-        <v>0.1832</v>
+        <v>0.1993</v>
       </c>
       <c r="S87">
-        <v>0.1105</v>
+        <v>0.1321</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:11.9% / 2-1:9.8%</t>
+          <t>2-0:11.8% / 1-0:11.7% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="V87">
-        <v>69.75</v>
+        <v>83.92</v>
       </c>
       <c r="W87" t="inlineStr">
         <is>
@@ -9112,14 +9112,14 @@
         </is>
       </c>
       <c r="X87">
-        <v>-0.0558</v>
+        <v>-0.0731</v>
       </c>
       <c r="Y87">
         <v>0</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>周六017</t>
+          <t>周六021</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>赫罗纳 对 埃尔切</t>
+          <t>赫塔费 对 奥萨苏纳</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9190,44 +9190,44 @@
         </is>
       </c>
       <c r="K88">
-        <v>0.5348</v>
+        <v>0.3645</v>
       </c>
       <c r="L88">
-        <v>0.2446</v>
+        <v>0.3543</v>
       </c>
       <c r="M88">
-        <v>0.2206</v>
+        <v>0.2812</v>
       </c>
       <c r="N88">
-        <v>0.5348</v>
+        <v>0.3645</v>
       </c>
       <c r="O88">
-        <v>0.2446</v>
+        <v>0.3543</v>
       </c>
       <c r="P88">
-        <v>0.2206</v>
+        <v>0.2812</v>
       </c>
       <c r="Q88">
-        <v>0.6805</v>
+        <v>0.4219</v>
       </c>
       <c r="R88">
-        <v>0.1961</v>
+        <v>0.2649</v>
       </c>
       <c r="S88">
-        <v>0.1235</v>
+        <v>0.3132</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>2-0:12.7% / 1-0:12.1% / 1-1:9.5%</t>
+          <t>1-1:12.5% / 1-0:10.9% / 0-1:9.1%</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V88">
-        <v>57.62</v>
+        <v>20.86</v>
       </c>
       <c r="W88" t="inlineStr">
         <is>
@@ -9235,14 +9235,14 @@
         </is>
       </c>
       <c r="X88">
-        <v>-0.0534</v>
+        <v>-0.1143</v>
       </c>
       <c r="Y88">
         <v>0</v>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>周六018</t>
+          <t>周六022</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>马洛卡 对 奥维耶多</t>
+          <t>塞尔塔 对 塞维利亚</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9313,35 +9313,35 @@
         </is>
       </c>
       <c r="K89">
-        <v>0.6344</v>
+        <v>0.5438</v>
       </c>
       <c r="L89">
-        <v>0.2207</v>
+        <v>0.2578</v>
       </c>
       <c r="M89">
-        <v>0.1449</v>
+        <v>0.1984</v>
       </c>
       <c r="N89">
-        <v>0.6344</v>
+        <v>0.5438</v>
       </c>
       <c r="O89">
-        <v>0.2207</v>
+        <v>0.2578</v>
       </c>
       <c r="P89">
-        <v>0.1449</v>
+        <v>0.1984</v>
       </c>
       <c r="Q89">
-        <v>0.7056</v>
+        <v>0.6248</v>
       </c>
       <c r="R89">
-        <v>0.1837</v>
+        <v>0.2125</v>
       </c>
       <c r="S89">
-        <v>0.1108</v>
+        <v>0.1627</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>2-0:13% / 1-0:11.6% / 3-0:9.7%</t>
+          <t>2-0:11.3% / 1-0:11.2% / 2-1:10.1%</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9350,7 +9350,7 @@
         </is>
       </c>
       <c r="V89">
-        <v>75.91</v>
+        <v>62.09</v>
       </c>
       <c r="W89" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="X89">
-        <v>-0.07</v>
+        <v>-0.0538</v>
       </c>
       <c r="Y89">
         <v>0</v>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>周六019</t>
+          <t>周六023</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>西班牙人 对 皇家社会</t>
+          <t>阿拉维斯 对 巴列卡诺</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -9436,35 +9436,35 @@
         </is>
       </c>
       <c r="K90">
-        <v>0.4218</v>
+        <v>0.3919</v>
       </c>
       <c r="L90">
-        <v>0.3097</v>
+        <v>0.3108</v>
       </c>
       <c r="M90">
-        <v>0.2684</v>
+        <v>0.2972</v>
       </c>
       <c r="N90">
-        <v>0.4218</v>
+        <v>0.3919</v>
       </c>
       <c r="O90">
-        <v>0.3097</v>
+        <v>0.3108</v>
       </c>
       <c r="P90">
-        <v>0.2684</v>
+        <v>0.2972</v>
       </c>
       <c r="Q90">
-        <v>0.5114</v>
+        <v>0.4308</v>
       </c>
       <c r="R90">
-        <v>0.2489</v>
+        <v>0.2585</v>
       </c>
       <c r="S90">
-        <v>0.2398</v>
+        <v>0.3108</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1-1:11.8% / 1-0:11.3% / 2-1:9.4%</t>
+          <t>1-1:12.4% / 1-0:10.4% / 2-1:8.8%</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -9473,7 +9473,7 @@
         </is>
       </c>
       <c r="V90">
-        <v>31.71</v>
+        <v>30.97</v>
       </c>
       <c r="W90" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="X90">
-        <v>-0.1142</v>
+        <v>-0.1143</v>
       </c>
       <c r="Y90">
         <v>0</v>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>周六020</t>
+          <t>周六024</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9525,69 +9525,69 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>皇马 对 毕尔巴鄂</t>
+          <t>巴伦西亚 对 巴萨</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
+          <t>平局-客胜</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
           <t>主胜-主胜</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>主胜-平局</t>
-        </is>
-      </c>
       <c r="K91">
-        <v>0.6459</v>
+        <v>0.2639</v>
       </c>
       <c r="L91">
-        <v>0.1991</v>
+        <v>0.2353</v>
       </c>
       <c r="M91">
-        <v>0.155</v>
+        <v>0.5008</v>
       </c>
       <c r="N91">
-        <v>0.6459</v>
+        <v>0.2639</v>
       </c>
       <c r="O91">
-        <v>0.1991</v>
+        <v>0.2353</v>
       </c>
       <c r="P91">
-        <v>0.155</v>
+        <v>0.5008</v>
       </c>
       <c r="Q91">
-        <v>0.7118</v>
+        <v>0.2184</v>
       </c>
       <c r="R91">
-        <v>0.1812</v>
+        <v>0.2355</v>
       </c>
       <c r="S91">
-        <v>0.1071</v>
+        <v>0.5462</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>2-0:13.1% / 1-0:12% / 3-0:9.4%</t>
+          <t>1-1:11.3% / 0-1:11% / 1-2:9.6%</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="V91">
-        <v>79.72</v>
+        <v>54.58</v>
       </c>
       <c r="W91" t="inlineStr">
         <is>
@@ -9604,14 +9604,14 @@
         </is>
       </c>
       <c r="X91">
-        <v>-0.0731</v>
+        <v>-0.073</v>
       </c>
       <c r="Y91">
         <v>0</v>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>周六021</t>
+          <t>周六025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>赫塔费 对 奥萨苏纳</t>
+          <t>贝蒂斯 对 莱万特</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -9678,48 +9678,48 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K92">
-        <v>0.3645</v>
+        <v>0.416</v>
       </c>
       <c r="L92">
-        <v>0.3543</v>
+        <v>0.2888</v>
       </c>
       <c r="M92">
-        <v>0.2812</v>
+        <v>0.2951</v>
       </c>
       <c r="N92">
-        <v>0.3645</v>
+        <v>0.416</v>
       </c>
       <c r="O92">
-        <v>0.3543</v>
+        <v>0.2888</v>
       </c>
       <c r="P92">
-        <v>0.2812</v>
+        <v>0.2951</v>
       </c>
       <c r="Q92">
-        <v>0.444</v>
+        <v>0.4508</v>
       </c>
       <c r="R92">
-        <v>0.2626</v>
+        <v>0.2607</v>
       </c>
       <c r="S92">
-        <v>0.2935</v>
+        <v>0.2886</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1-1:12.5% / 1-0:11.5% / 2-1:8.8%</t>
+          <t>1-1:12.4% / 1-0:10.6% / 2-1:9.1%</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V92">
-        <v>16.66</v>
+        <v>38.03</v>
       </c>
       <c r="W92" t="inlineStr">
         <is>
@@ -9727,14 +9727,14 @@
         </is>
       </c>
       <c r="X92">
-        <v>-0.1143</v>
+        <v>-0.0557</v>
       </c>
       <c r="Y92">
         <v>0</v>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -9761,17 +9761,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>周六022</t>
+          <t>周六026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>塞尔塔 对 塞维利亚</t>
+          <t>明尼苏达 对 盐湖城</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9801,39 +9801,39 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K93">
-        <v>0.5438</v>
+        <v>0.4291</v>
       </c>
       <c r="L93">
-        <v>0.2578</v>
+        <v>0.2591</v>
       </c>
       <c r="M93">
-        <v>0.1984</v>
+        <v>0.3118</v>
       </c>
       <c r="N93">
-        <v>0.5438</v>
+        <v>0.4291</v>
       </c>
       <c r="O93">
-        <v>0.2578</v>
+        <v>0.2591</v>
       </c>
       <c r="P93">
-        <v>0.1984</v>
+        <v>0.3118</v>
       </c>
       <c r="Q93">
-        <v>0.7044</v>
+        <v>0.4532</v>
       </c>
       <c r="R93">
-        <v>0.1873</v>
+        <v>0.251</v>
       </c>
       <c r="S93">
-        <v>0.1083</v>
+        <v>0.2958</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>2-0:13.4% / 1-0:12.5% / 2-1:9.6%</t>
+          <t>1-1:11.8% / 1-0:10.5% / 2-1:9%</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="V93">
-        <v>57.89</v>
+        <v>38.65</v>
       </c>
       <c r="W93" t="inlineStr">
         <is>
@@ -9850,14 +9850,14 @@
         </is>
       </c>
       <c r="X93">
-        <v>-0.0538</v>
+        <v>-0.0813</v>
       </c>
       <c r="Y93">
         <v>0</v>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -9884,17 +9884,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>周六023</t>
+          <t>周六027</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>阿拉维斯 对 巴列卡诺</t>
+          <t>夏洛特FC 对 新英格兰</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9928,35 +9928,35 @@
         </is>
       </c>
       <c r="K94">
-        <v>0.3919</v>
+        <v>0.4926</v>
       </c>
       <c r="L94">
-        <v>0.3108</v>
+        <v>0.2556</v>
       </c>
       <c r="M94">
-        <v>0.2972</v>
+        <v>0.2518</v>
       </c>
       <c r="N94">
-        <v>0.3919</v>
+        <v>0.4926</v>
       </c>
       <c r="O94">
-        <v>0.3108</v>
+        <v>0.2556</v>
       </c>
       <c r="P94">
-        <v>0.2972</v>
+        <v>0.2518</v>
       </c>
       <c r="Q94">
-        <v>0.4561</v>
+        <v>0.5474</v>
       </c>
       <c r="R94">
-        <v>0.2581</v>
+        <v>0.2347</v>
       </c>
       <c r="S94">
-        <v>0.2859</v>
+        <v>0.218</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1-1:12.3% / 1-0:10.7% / 2-1:9.1%</t>
+          <t>1-0:11.4% / 1-1:11.1% / 2-1:10%</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="V94">
-        <v>26.77</v>
+        <v>54</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
@@ -9973,14 +9973,14 @@
         </is>
       </c>
       <c r="X94">
-        <v>-0.1143</v>
+        <v>-0.0813</v>
       </c>
       <c r="Y94">
         <v>0</v>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10007,79 +10007,79 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>周六024</t>
+          <t>周六028</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>巴伦西亚 对 巴萨</t>
+          <t>华盛顿 对 蒙特利尔</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K95">
-        <v>0.2639</v>
+        <v>0.4848</v>
       </c>
       <c r="L95">
-        <v>0.2353</v>
+        <v>0.2592</v>
       </c>
       <c r="M95">
-        <v>0.5008</v>
+        <v>0.256</v>
       </c>
       <c r="N95">
-        <v>0.2639</v>
+        <v>0.4848</v>
       </c>
       <c r="O95">
-        <v>0.2353</v>
+        <v>0.2592</v>
       </c>
       <c r="P95">
-        <v>0.5008</v>
+        <v>0.256</v>
       </c>
       <c r="Q95">
-        <v>0.175</v>
+        <v>0.5353</v>
       </c>
       <c r="R95">
-        <v>0.2191</v>
+        <v>0.2374</v>
       </c>
       <c r="S95">
-        <v>0.606</v>
+        <v>0.2274</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>0-1:11.7% / 0-2:10.8% / 1-1:10.3%</t>
+          <t>1-1:11.3% / 1-0:10.9% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="V95">
-        <v>50.38</v>
+        <v>52.41</v>
       </c>
       <c r="W95" t="inlineStr">
         <is>
@@ -10096,14 +10096,14 @@
         </is>
       </c>
       <c r="X95">
-        <v>-0.073</v>
+        <v>-0.0803</v>
       </c>
       <c r="Y95">
         <v>0</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10130,17 +10130,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>周六025</t>
+          <t>周六029</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>美职</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>贝蒂斯 对 莱万特</t>
+          <t>纳什维尔 对 纽约城</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -10170,39 +10170,39 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>平局-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K96">
-        <v>0.416</v>
+        <v>0.5639</v>
       </c>
       <c r="L96">
-        <v>0.2888</v>
+        <v>0.2393</v>
       </c>
       <c r="M96">
-        <v>0.2951</v>
+        <v>0.1968</v>
       </c>
       <c r="N96">
-        <v>0.416</v>
+        <v>0.5639</v>
       </c>
       <c r="O96">
-        <v>0.2888</v>
+        <v>0.2393</v>
       </c>
       <c r="P96">
-        <v>0.2951</v>
+        <v>0.1968</v>
       </c>
       <c r="Q96">
-        <v>0.4813</v>
+        <v>0.6454</v>
       </c>
       <c r="R96">
-        <v>0.2548</v>
+        <v>0.2031</v>
       </c>
       <c r="S96">
-        <v>0.264</v>
+        <v>0.1516</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1-1:12.1% / 1-0:10.9% / 2-1:9.3%</t>
+          <t>2-0:11.6% / 1-0:11.4% / 2-1:9.7%</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="V96">
-        <v>33.83</v>
+        <v>65.26</v>
       </c>
       <c r="W96" t="inlineStr">
         <is>
@@ -10219,14 +10219,14 @@
         </is>
       </c>
       <c r="X96">
-        <v>-0.0557</v>
+        <v>-0.1147</v>
       </c>
       <c r="Y96">
         <v>0</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>周六026</t>
+          <t>周六030</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>明尼苏达 对 盐湖城</t>
+          <t>波特兰 对 圣何塞</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -10297,44 +10297,44 @@
         </is>
       </c>
       <c r="K97">
-        <v>0.4291</v>
+        <v>0.3987</v>
       </c>
       <c r="L97">
-        <v>0.2591</v>
+        <v>0.2408</v>
       </c>
       <c r="M97">
-        <v>0.3118</v>
+        <v>0.3605</v>
       </c>
       <c r="N97">
-        <v>0.4291</v>
+        <v>0.3987</v>
       </c>
       <c r="O97">
-        <v>0.2591</v>
+        <v>0.2408</v>
       </c>
       <c r="P97">
-        <v>0.3118</v>
+        <v>0.3605</v>
       </c>
       <c r="Q97">
-        <v>0.4828</v>
+        <v>0.4014</v>
       </c>
       <c r="R97">
-        <v>0.2442</v>
+        <v>0.2565</v>
       </c>
       <c r="S97">
-        <v>0.273</v>
+        <v>0.3422</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1-1:11.7% / 1-0:10.8% / 2-1:9.6%</t>
+          <t>1-1:12.4% / 1-0:10% / 0-1:8.7%</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V97">
-        <v>34.45</v>
+        <v>27.59</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
@@ -10342,14 +10342,14 @@
         </is>
       </c>
       <c r="X97">
-        <v>-0.0813</v>
+        <v>-0.079</v>
       </c>
       <c r="Y97">
         <v>0</v>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：美职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>周六027</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>英冠</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>夏洛特FC 对 新英格兰</t>
+          <t>赫尔城 对 南安普敦</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10420,35 +10420,35 @@
         </is>
       </c>
       <c r="K98">
-        <v>0.4926</v>
+        <v>0.6828</v>
       </c>
       <c r="L98">
-        <v>0.2556</v>
+        <v>0.1762</v>
       </c>
       <c r="M98">
-        <v>0.2518</v>
+        <v>0.141</v>
       </c>
       <c r="N98">
-        <v>0.4926</v>
+        <v>0.6828</v>
       </c>
       <c r="O98">
-        <v>0.2556</v>
+        <v>0.1762</v>
       </c>
       <c r="P98">
-        <v>0.2518</v>
+        <v>0.141</v>
       </c>
       <c r="Q98">
-        <v>0.6088</v>
+        <v>0.6733</v>
       </c>
       <c r="R98">
-        <v>0.2245</v>
+        <v>0.1961</v>
       </c>
       <c r="S98">
-        <v>0.1667</v>
+        <v>0.1307</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1-0:12.4% / 1-1:10.8% / 2-0:10.6%</t>
+          <t>2-0:12% / 1-0:11% / 2-1:9.6%</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="V98">
-        <v>49.8</v>
+        <v>89.16</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
@@ -10465,14 +10465,14 @@
         </is>
       </c>
       <c r="X98">
-        <v>-0.0813</v>
+        <v>-0.0741</v>
       </c>
       <c r="Y98">
         <v>0</v>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：英冠，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10499,17 +10499,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>周六028</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>德国杯</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>华盛顿 对 蒙特利尔</t>
+          <t>拜仁慕尼黑 对 斯图加特</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10543,35 +10543,35 @@
         </is>
       </c>
       <c r="K99">
-        <v>0.4848</v>
+        <v>0.7045</v>
       </c>
       <c r="L99">
-        <v>0.2592</v>
+        <v>0.1655</v>
       </c>
       <c r="M99">
-        <v>0.256</v>
+        <v>0.13</v>
       </c>
       <c r="N99">
-        <v>0.4848</v>
+        <v>0.2543</v>
       </c>
       <c r="O99">
-        <v>0.2592</v>
+        <v>0.2447</v>
       </c>
       <c r="P99">
-        <v>0.256</v>
+        <v>0.501</v>
       </c>
       <c r="Q99">
-        <v>0.5995</v>
+        <v>0.215</v>
       </c>
       <c r="R99">
-        <v>0.2227</v>
+        <v>0.2374</v>
       </c>
       <c r="S99">
-        <v>0.1779</v>
+        <v>0.5477</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1-0:11.7% / 2-0:11% / 1-1:10.6%</t>
+          <t>1-1:11.4% / 0-1:10.8% / 1-2:10%</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="V99">
-        <v>48.21</v>
+        <v>96.43</v>
       </c>
       <c r="W99" t="inlineStr">
         <is>
@@ -10588,14 +10588,14 @@
         </is>
       </c>
       <c r="X99">
-        <v>-0.0803</v>
+        <v>-0.0566</v>
       </c>
       <c r="Y99">
         <v>0</v>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -10622,79 +10622,79 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>周六029</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>纳什维尔 对 纽约城</t>
+          <t>博洛尼亚 对 国际米兰</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
+          <t>客胜</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>主胜</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>平局-主胜</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="K100">
-        <v>0.5639</v>
+        <v>0.3001</v>
       </c>
       <c r="L100">
-        <v>0.2393</v>
+        <v>0.2529</v>
       </c>
       <c r="M100">
-        <v>0.1968</v>
+        <v>0.447</v>
       </c>
       <c r="N100">
-        <v>0.5639</v>
+        <v>0.627</v>
       </c>
       <c r="O100">
-        <v>0.2393</v>
+        <v>0.2197</v>
       </c>
       <c r="P100">
-        <v>0.1968</v>
+        <v>0.1532</v>
       </c>
       <c r="Q100">
-        <v>0.7065</v>
+        <v>0.664</v>
       </c>
       <c r="R100">
-        <v>0.1848</v>
+        <v>0.2009</v>
       </c>
       <c r="S100">
-        <v>0.1088</v>
+        <v>0.1352</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2-0:13.5% / 1-0:12.1% / 2-1:9.2%</t>
+          <t>2-0:12.1% / 1-0:11.5% / 1-1:9.8%</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="V100">
-        <v>61.06</v>
+        <v>40.86</v>
       </c>
       <c r="W100" t="inlineStr">
         <is>
@@ -10711,14 +10711,14 @@
         </is>
       </c>
       <c r="X100">
-        <v>-0.1147</v>
+        <v>-0.0651</v>
       </c>
       <c r="Y100">
         <v>0</v>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10745,17 +10745,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>周六030</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>美职</t>
+          <t>意甲</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>波特兰 对 圣何塞</t>
+          <t>拉齐奥 对 比萨</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -10765,17 +10765,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10785,48 +10785,48 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K101">
-        <v>0.3987</v>
+        <v>0.6014</v>
       </c>
       <c r="L101">
-        <v>0.2408</v>
+        <v>0.2297</v>
       </c>
       <c r="M101">
-        <v>0.3605</v>
+        <v>0.1689</v>
       </c>
       <c r="N101">
-        <v>0.3987</v>
+        <v>0.4947</v>
       </c>
       <c r="O101">
-        <v>0.2408</v>
+        <v>0.2664</v>
       </c>
       <c r="P101">
-        <v>0.3605</v>
+        <v>0.239</v>
       </c>
       <c r="Q101">
-        <v>0.4109</v>
+        <v>0.5547</v>
       </c>
       <c r="R101">
-        <v>0.2562</v>
+        <v>0.2313</v>
       </c>
       <c r="S101">
-        <v>0.333</v>
+        <v>0.214</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:10% / 2-1:9%</t>
+          <t>1-0:10.9% / 1-1:10.7% / 2-0:10%</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V101">
-        <v>23.39</v>
+        <v>73.95</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
@@ -10834,14 +10834,14 @@
         </is>
       </c>
       <c r="X101">
-        <v>-0.079</v>
+        <v>-0.065</v>
       </c>
       <c r="Y101">
         <v>0</v>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>经模型综合分析：美职，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10868,17 +10868,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>英冠</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>赫尔城 对 南安普敦</t>
+          <t>维戈塞尔塔 对 塞维利亚</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -10912,35 +10912,35 @@
         </is>
       </c>
       <c r="K102">
-        <v>0.6828</v>
+        <v>0.5438</v>
       </c>
       <c r="L102">
-        <v>0.1762</v>
+        <v>0.2578</v>
       </c>
       <c r="M102">
-        <v>0.141</v>
+        <v>0.1984</v>
       </c>
       <c r="N102">
-        <v>0.6828</v>
+        <v>0.3949</v>
       </c>
       <c r="O102">
-        <v>0.1762</v>
+        <v>0.3331</v>
       </c>
       <c r="P102">
-        <v>0.141</v>
+        <v>0.272</v>
       </c>
       <c r="Q102">
-        <v>0.7109</v>
+        <v>0.4509</v>
       </c>
       <c r="R102">
-        <v>0.1796</v>
+        <v>0.2595</v>
       </c>
       <c r="S102">
-        <v>0.1096</v>
+        <v>0.2896</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>2-0:12.9% / 1-0:11.7% / 3-0:9.4%</t>
+          <t>1-1:12.3% / 1-0:10.9% / 2-1:8.9%</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="V102">
-        <v>84.96</v>
+        <v>62.09</v>
       </c>
       <c r="W102" t="inlineStr">
         <is>
@@ -10957,14 +10957,14 @@
         </is>
       </c>
       <c r="X102">
-        <v>-0.0741</v>
+        <v>-0.0645</v>
       </c>
       <c r="Y102">
         <v>0</v>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>经模型综合分析：英冠，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>德国杯</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>拜仁慕尼黑 对 斯图加特</t>
+          <t>赫塔费 对 奥萨苏纳</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -11016,17 +11016,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-主胜</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11035,44 +11035,44 @@
         </is>
       </c>
       <c r="K103">
-        <v>0.7045</v>
+        <v>0.3645</v>
       </c>
       <c r="L103">
-        <v>0.1655</v>
+        <v>0.3543</v>
       </c>
       <c r="M103">
-        <v>0.13</v>
+        <v>0.2812</v>
       </c>
       <c r="N103">
-        <v>0.2543</v>
+        <v>0.5101</v>
       </c>
       <c r="O103">
-        <v>0.2447</v>
+        <v>0.2496</v>
       </c>
       <c r="P103">
-        <v>0.501</v>
+        <v>0.2402</v>
       </c>
       <c r="Q103">
-        <v>0.1602</v>
+        <v>0.5728</v>
       </c>
       <c r="R103">
-        <v>0.2225</v>
+        <v>0.229</v>
       </c>
       <c r="S103">
-        <v>0.6174</v>
+        <v>0.1982</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>0-1:11.6% / 0-2:11.4% / 1-1:10.8%</t>
+          <t>1-0:11.3% / 1-1:10.9% / 2-0:10.3%</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V103">
-        <v>92.23</v>
+        <v>20.86</v>
       </c>
       <c r="W103" t="inlineStr">
         <is>
@@ -11080,14 +11080,14 @@
         </is>
       </c>
       <c r="X103">
-        <v>-0.0566</v>
+        <v>-0.066</v>
       </c>
       <c r="Y103">
         <v>0</v>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>经模型综合分析：德国杯，客胜概率领先主胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六014 胜平负方向强制一致</t>
+          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11114,79 +11114,79 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>西甲</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>博洛尼亚 对 国际米兰</t>
+          <t>赫罗纳 对 埃尔切</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>主胜</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>主胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-主胜</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>主胜-主胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K104">
-        <v>0.3001</v>
+        <v>0.5348</v>
       </c>
       <c r="L104">
-        <v>0.2529</v>
+        <v>0.2446</v>
       </c>
       <c r="M104">
-        <v>0.447</v>
+        <v>0.2206</v>
       </c>
       <c r="N104">
-        <v>0.627</v>
+        <v>0.4605</v>
       </c>
       <c r="O104">
-        <v>0.2197</v>
+        <v>0.2536</v>
       </c>
       <c r="P104">
-        <v>0.1532</v>
+        <v>0.2859</v>
       </c>
       <c r="Q104">
-        <v>0.7036</v>
+        <v>0.4946</v>
       </c>
       <c r="R104">
-        <v>0.188</v>
+        <v>0.2511</v>
       </c>
       <c r="S104">
-        <v>0.1084</v>
+        <v>0.2543</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>2-0:13.3% / 1-0:11.9% / 3-0:9.6%</t>
+          <t>1-1:11.9% / 1-0:10.8% / 2-1:9.4%</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -11195,7 +11195,7 @@
         </is>
       </c>
       <c r="V104">
-        <v>36.66</v>
+        <v>61.82</v>
       </c>
       <c r="W104" t="inlineStr">
         <is>
@@ -11203,14 +11203,14 @@
         </is>
       </c>
       <c r="X104">
-        <v>-0.0651</v>
+        <v>-0.0606</v>
       </c>
       <c r="Y104">
         <v>0</v>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六013 胜平负方向强制一致</t>
+          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11237,17 +11237,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>意甲</t>
+          <t>荷乙</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>拉齐奥 对 比萨</t>
+          <t>福伦丹 对 威廉二世</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11257,17 +11257,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -11277,39 +11277,39 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K105">
-        <v>0.6014</v>
+        <v>0.4352</v>
       </c>
       <c r="L105">
-        <v>0.2297</v>
+        <v>0.2643</v>
       </c>
       <c r="M105">
-        <v>0.1689</v>
+        <v>0.3005</v>
       </c>
       <c r="N105">
-        <v>0.4947</v>
+        <v>0.3999</v>
       </c>
       <c r="O105">
-        <v>0.2664</v>
+        <v>0.2717</v>
       </c>
       <c r="P105">
-        <v>0.239</v>
+        <v>0.3284</v>
       </c>
       <c r="Q105">
-        <v>0.6228</v>
+        <v>0.4197</v>
       </c>
       <c r="R105">
-        <v>0.2126</v>
+        <v>0.2589</v>
       </c>
       <c r="S105">
-        <v>0.1647</v>
+        <v>0.3215</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1-0:11.9% / 2-0:11.6% / 1-1:9.9%</t>
+          <t>1-1:12.3% / 1-0:9.7% / 2-1:8.9%</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="V105">
-        <v>69.75</v>
+        <v>40.66</v>
       </c>
       <c r="W105" t="inlineStr">
         <is>
@@ -11326,14 +11326,14 @@
         </is>
       </c>
       <c r="X105">
-        <v>-0.065</v>
+        <v>-0.079</v>
       </c>
       <c r="Y105">
         <v>0</v>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>经模型综合分析：意甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六016 胜平负方向强制一致</t>
+          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11360,17 +11360,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>维戈塞尔塔 对 塞维利亚</t>
+          <t>哈尔姆斯塔德 对 厄尔格里特</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -11400,39 +11400,39 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>主胜-平局</t>
+          <t>客胜-客胜</t>
         </is>
       </c>
       <c r="K106">
-        <v>0.5438</v>
+        <v>0.4354</v>
       </c>
       <c r="L106">
-        <v>0.2578</v>
+        <v>0.2737</v>
       </c>
       <c r="M106">
-        <v>0.1984</v>
+        <v>0.291</v>
       </c>
       <c r="N106">
-        <v>0.3949</v>
+        <v>0.4354</v>
       </c>
       <c r="O106">
-        <v>0.3331</v>
+        <v>0.2737</v>
       </c>
       <c r="P106">
-        <v>0.272</v>
+        <v>0.291</v>
       </c>
       <c r="Q106">
-        <v>0.482</v>
+        <v>0.4732</v>
       </c>
       <c r="R106">
-        <v>0.2551</v>
+        <v>0.2512</v>
       </c>
       <c r="S106">
-        <v>0.2629</v>
+        <v>0.2757</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>1-1:12.2% / 1-0:11.4% / 2-1:9.4%</t>
+          <t>1-1:12.3% / 1-0:10.7% / 2-1:9%</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="V106">
-        <v>57.89</v>
+        <v>38.74</v>
       </c>
       <c r="W106" t="inlineStr">
         <is>
@@ -11449,14 +11449,14 @@
         </is>
       </c>
       <c r="X106">
-        <v>-0.0645</v>
+        <v>-0.0804</v>
       </c>
       <c r="Y106">
         <v>0</v>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六022 胜平负方向强制一致</t>
+          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11483,17 +11483,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>瑞超</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>赫塔费 对 奥萨苏纳</t>
+          <t>卡尔马 对 代格福什</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11527,44 +11527,44 @@
         </is>
       </c>
       <c r="K107">
-        <v>0.3645</v>
+        <v>0.4445</v>
       </c>
       <c r="L107">
-        <v>0.3543</v>
+        <v>0.291</v>
       </c>
       <c r="M107">
-        <v>0.2812</v>
+        <v>0.2645</v>
       </c>
       <c r="N107">
-        <v>0.5101</v>
+        <v>0.4445</v>
       </c>
       <c r="O107">
-        <v>0.2496</v>
+        <v>0.291</v>
       </c>
       <c r="P107">
-        <v>0.2402</v>
+        <v>0.2645</v>
       </c>
       <c r="Q107">
-        <v>0.6407</v>
+        <v>0.5028</v>
       </c>
       <c r="R107">
-        <v>0.2083</v>
+        <v>0.2467</v>
       </c>
       <c r="S107">
-        <v>0.1511</v>
+        <v>0.2505</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1-0:12.4% / 2-0:12% / 1-1:10.1%</t>
+          <t>1-1:11.9% / 1-0:11% / 2-1:9.7%</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="V107">
-        <v>16.66</v>
+        <v>40.22</v>
       </c>
       <c r="W107" t="inlineStr">
         <is>
@@ -11572,14 +11572,14 @@
         </is>
       </c>
       <c r="X107">
-        <v>-0.066</v>
+        <v>-0.0812</v>
       </c>
       <c r="Y107">
         <v>0</v>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六021 胜平负方向强制一致</t>
+          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11606,17 +11606,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>西甲</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>赫罗纳 对 埃尔切</t>
+          <t>坦佩雷山猫 对 赫尔辛基火花</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11650,44 +11650,44 @@
         </is>
       </c>
       <c r="K108">
-        <v>0.5348</v>
+        <v>0.521</v>
       </c>
       <c r="L108">
-        <v>0.2446</v>
+        <v>0.2408</v>
       </c>
       <c r="M108">
-        <v>0.2206</v>
+        <v>0.2382</v>
       </c>
       <c r="N108">
-        <v>0.4605</v>
+        <v>0.521</v>
       </c>
       <c r="O108">
-        <v>0.2536</v>
+        <v>0.2408</v>
       </c>
       <c r="P108">
-        <v>0.2859</v>
+        <v>0.2382</v>
       </c>
       <c r="Q108">
-        <v>0.5475</v>
+        <v>0.5786</v>
       </c>
       <c r="R108">
-        <v>0.2369</v>
+        <v>0.2293</v>
       </c>
       <c r="S108">
-        <v>0.2157</v>
+        <v>0.1921</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1-0:11.4% / 1-1:11% / 2-1:9.9%</t>
+          <t>1-0:11.5% / 1-1:11.3% / 2-0:10%</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V108">
-        <v>57.62</v>
+        <v>55.38</v>
       </c>
       <c r="W108" t="inlineStr">
         <is>
@@ -11695,14 +11695,14 @@
         </is>
       </c>
       <c r="X108">
-        <v>-0.0606</v>
+        <v>-0.0737</v>
       </c>
       <c r="Y108">
         <v>0</v>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>经模型综合分析：西甲，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六017 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11729,17 +11729,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>荷乙</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>福伦丹 对 威廉二世</t>
+          <t>雅罗 对 玛丽港</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -11769,39 +11769,39 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>主胜-平局</t>
         </is>
       </c>
       <c r="K109">
-        <v>0.4352</v>
+        <v>0.4923</v>
       </c>
       <c r="L109">
-        <v>0.2643</v>
+        <v>0.2635</v>
       </c>
       <c r="M109">
-        <v>0.3005</v>
+        <v>0.2441</v>
       </c>
       <c r="N109">
-        <v>0.3999</v>
+        <v>0.4923</v>
       </c>
       <c r="O109">
-        <v>0.2717</v>
+        <v>0.2635</v>
       </c>
       <c r="P109">
-        <v>0.3284</v>
+        <v>0.2441</v>
       </c>
       <c r="Q109">
-        <v>0.44</v>
+        <v>0.5468</v>
       </c>
       <c r="R109">
-        <v>0.2542</v>
+        <v>0.2355</v>
       </c>
       <c r="S109">
-        <v>0.3059</v>
+        <v>0.2178</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1-1:11.9% / 1-0:10.1% / 2-1:9.2%</t>
+          <t>1-0:11.3% / 1-1:10.9% / 2-0:9.8%</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -11810,7 +11810,7 @@
         </is>
       </c>
       <c r="V109">
-        <v>36.46</v>
+        <v>50.44</v>
       </c>
       <c r="W109" t="inlineStr">
         <is>
@@ -11818,14 +11818,14 @@
         </is>
       </c>
       <c r="X109">
-        <v>-0.079</v>
+        <v>-0.0814</v>
       </c>
       <c r="Y109">
         <v>0</v>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>经模型综合分析：荷乙，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六015 胜平负方向强制一致</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -11852,17 +11852,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>哈尔姆斯塔德 对 厄尔格里特</t>
+          <t>库奥皮奥 对 拉赫蒂</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>客胜</t>
+          <t>平局</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -11892,39 +11892,39 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>客胜-客胜</t>
+          <t>平局-平局</t>
         </is>
       </c>
       <c r="K110">
-        <v>0.4354</v>
+        <v>0.5759</v>
       </c>
       <c r="L110">
-        <v>0.2737</v>
+        <v>0.2432</v>
       </c>
       <c r="M110">
-        <v>0.291</v>
+        <v>0.181</v>
       </c>
       <c r="N110">
-        <v>0.4354</v>
+        <v>0.5759</v>
       </c>
       <c r="O110">
-        <v>0.2737</v>
+        <v>0.2432</v>
       </c>
       <c r="P110">
-        <v>0.291</v>
+        <v>0.181</v>
       </c>
       <c r="Q110">
-        <v>0.511</v>
+        <v>0.6591</v>
       </c>
       <c r="R110">
-        <v>0.2464</v>
+        <v>0.1991</v>
       </c>
       <c r="S110">
-        <v>0.2427</v>
+        <v>0.1419</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>1-1:12% / 1-0:11.3% / 2-1:9.2%</t>
+          <t>1-0:11.8% / 2-0:11.5% / 2-1:9.8%</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -11933,7 +11933,7 @@
         </is>
       </c>
       <c r="V110">
-        <v>34.54</v>
+        <v>65.81</v>
       </c>
       <c r="W110" t="inlineStr">
         <is>
@@ -11941,14 +11941,14 @@
         </is>
       </c>
       <c r="X110">
-        <v>-0.0804</v>
+        <v>-0.0837</v>
       </c>
       <c r="Y110">
         <v>0</v>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先客胜；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11975,17 +11975,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>瑞超</t>
+          <t>芬超</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>卡尔马 对 代格福什</t>
+          <t>塞伊奈约基 对 AC 奥卢</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>平局</t>
+          <t>客胜</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -12015,48 +12015,48 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>平局-平局</t>
+          <t>平局-客胜</t>
         </is>
       </c>
       <c r="K111">
-        <v>0.4445</v>
+        <v>0.369</v>
       </c>
       <c r="L111">
-        <v>0.291</v>
+        <v>0.2689</v>
       </c>
       <c r="M111">
-        <v>0.2645</v>
+        <v>0.362</v>
       </c>
       <c r="N111">
-        <v>0.4445</v>
+        <v>0.369</v>
       </c>
       <c r="O111">
-        <v>0.291</v>
+        <v>0.2689</v>
       </c>
       <c r="P111">
-        <v>0.2645</v>
+        <v>0.362</v>
       </c>
       <c r="Q111">
-        <v>0.5478</v>
+        <v>0.3744</v>
       </c>
       <c r="R111">
-        <v>0.2373</v>
+        <v>0.2614</v>
       </c>
       <c r="S111">
-        <v>0.2149</v>
+        <v>0.3643</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1-1:11.3% / 1-0:11.3% / 2-0:10.3%</t>
+          <t>1-1:12.4% / 1-0:9.5% / 0-1:9.1%</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="V111">
-        <v>36.02</v>
+        <v>19.85</v>
       </c>
       <c r="W111" t="inlineStr">
         <is>
@@ -12064,14 +12064,14 @@
         </is>
       </c>
       <c r="X111">
-        <v>-0.0812</v>
+        <v>-0.0834</v>
       </c>
       <c r="Y111">
         <v>0</v>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>经模型综合分析：瑞超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
+          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12085,504 +12085,12 @@
         </is>
       </c>
       <c r="AC111" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>坦佩雷山猫 对 赫尔辛基火花</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>平局-主胜</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>客胜-客胜</t>
-        </is>
-      </c>
-      <c r="K112">
-        <v>0.5009</v>
-      </c>
-      <c r="L112">
-        <v>0.2465</v>
-      </c>
-      <c r="M112">
-        <v>0.2526</v>
-      </c>
-      <c r="N112">
-        <v>0.521</v>
-      </c>
-      <c r="O112">
-        <v>0.2408</v>
-      </c>
-      <c r="P112">
-        <v>0.2382</v>
-      </c>
-      <c r="Q112">
-        <v>0.6562</v>
-      </c>
-      <c r="R112">
-        <v>0.2042</v>
-      </c>
-      <c r="S112">
-        <v>0.1396</v>
-      </c>
-      <c r="T112" t="inlineStr">
-        <is>
-          <t>1-0:12.4% / 2-0:11.8% / 1-1:10.2%</t>
-        </is>
-      </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="V112">
-        <v>51.41</v>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X112">
-        <v>-0.0737</v>
-      </c>
-      <c r="Y112">
-        <v>0</v>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六008 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>雅罗 对 玛丽港</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>平局-平局</t>
-        </is>
-      </c>
-      <c r="K113">
-        <v>0.4828</v>
-      </c>
-      <c r="L113">
-        <v>0.272</v>
-      </c>
-      <c r="M113">
-        <v>0.2452</v>
-      </c>
-      <c r="N113">
-        <v>0.4923</v>
-      </c>
-      <c r="O113">
-        <v>0.2635</v>
-      </c>
-      <c r="P113">
-        <v>0.2441</v>
-      </c>
-      <c r="Q113">
-        <v>0.615</v>
-      </c>
-      <c r="R113">
-        <v>0.2164</v>
-      </c>
-      <c r="S113">
-        <v>0.1687</v>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>1-0:12.1% / 2-0:11.7% / 1-1:10%</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="V113">
-        <v>46.73</v>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X113">
-        <v>-0.0814</v>
-      </c>
-      <c r="Y113">
-        <v>0</v>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六011 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>库奥皮奥 对 拉赫蒂</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>平局</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>主胜-主胜</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>平局-平局</t>
-        </is>
-      </c>
-      <c r="K114">
-        <v>0.5934</v>
-      </c>
-      <c r="L114">
-        <v>0.2361</v>
-      </c>
-      <c r="M114">
-        <v>0.1705</v>
-      </c>
-      <c r="N114">
-        <v>0.5759</v>
-      </c>
-      <c r="O114">
-        <v>0.2432</v>
-      </c>
-      <c r="P114">
-        <v>0.181</v>
-      </c>
-      <c r="Q114">
-        <v>0.7019</v>
-      </c>
-      <c r="R114">
-        <v>0.1851</v>
-      </c>
-      <c r="S114">
-        <v>0.113</v>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>2-0:12.6% / 1-0:12.5% / 3-0:9.6%</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="V114">
-        <v>67.88</v>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X114">
-        <v>-0.0837</v>
-      </c>
-      <c r="Y114">
-        <v>0</v>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先平局；风险中；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六010 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>芬超</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>塞伊奈约基 对 AC 奥卢</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>主胜</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>客胜</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>平局-主胜</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>客胜-客胜</t>
-        </is>
-      </c>
-      <c r="K115">
-        <v>0.3731</v>
-      </c>
-      <c r="L115">
-        <v>0.2676</v>
-      </c>
-      <c r="M115">
-        <v>0.3593</v>
-      </c>
-      <c r="N115">
-        <v>0.369</v>
-      </c>
-      <c r="O115">
-        <v>0.2689</v>
-      </c>
-      <c r="P115">
-        <v>0.362</v>
-      </c>
-      <c r="Q115">
-        <v>0.3796</v>
-      </c>
-      <c r="R115">
-        <v>0.2597</v>
-      </c>
-      <c r="S115">
-        <v>0.3607</v>
-      </c>
-      <c r="T115" t="inlineStr">
-        <is>
-          <t>1-1:12.4% / 1-0:9.5% / 0-1:9.2%</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="V115">
-        <v>19.36</v>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>观察/跳过</t>
-        </is>
-      </c>
-      <c r="X115">
-        <v>-0.0834</v>
-      </c>
-      <c r="Y115">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>经模型综合分析：芬超，主胜概率领先客胜；风险高；已接入本次实时赔率快照，并完成隐含概率换算与高级数据修正；同场次已与竞彩足球 周六009 胜平负方向强制一致</t>
-        </is>
-      </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD115"/>
+  <autoFilter ref="A1:AD111"/>
 </worksheet>
 </file>